--- a/reports/Inventory-Ageing-SKU-wise-2026-10-29.xlsx
+++ b/reports/Inventory-Ageing-SKU-wise-2026-10-29.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="196">
   <si>
     <t xml:space="preserve">Finished inventory ageing by section (MT) - as of 29-Oct-2026</t>
   </si>
@@ -201,6 +201,12 @@
     <t xml:space="preserve">SHS 150x150 x 5.0</t>
   </si>
   <si>
+    <t xml:space="preserve">RHS 145x82 x 4.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145x82</t>
+  </si>
+  <si>
     <t xml:space="preserve">RHS 96x48 x 2.5</t>
   </si>
   <si>
@@ -267,6 +273,9 @@
     <t xml:space="preserve">SHS 38x38 x 2.5</t>
   </si>
   <si>
+    <t xml:space="preserve">SHS 60x60 x 5.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">RHS 96x48 x 5.0</t>
   </si>
   <si>
@@ -312,6 +321,9 @@
     <t xml:space="preserve">CHS 50 NB x 3.2</t>
   </si>
   <si>
+    <t xml:space="preserve">RHS 145x82 x 3.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHS 80 NB x 2.0</t>
   </si>
   <si>
@@ -393,9 +405,6 @@
     <t xml:space="preserve">RHS 40x20 x 2.0</t>
   </si>
   <si>
-    <t xml:space="preserve">SHS 60x60 x 5.0</t>
-  </si>
-  <si>
     <t xml:space="preserve">RHS 100x50 x 3.0</t>
   </si>
   <si>
@@ -537,12 +546,6 @@
     <t xml:space="preserve">RHS 75x25 x 2.5</t>
   </si>
   <si>
-    <t xml:space="preserve">RHS 145x82 x 3.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145x82</t>
-  </si>
-  <si>
     <t xml:space="preserve">SHS 100x100 x 2.5</t>
   </si>
   <si>
@@ -555,9 +558,6 @@
     <t xml:space="preserve">75x75</t>
   </si>
   <si>
-    <t xml:space="preserve">RHS 145x82 x 4.0</t>
-  </si>
-  <si>
     <t xml:space="preserve">SHS 30x30 x 1.6</t>
   </si>
   <si>
@@ -604,6 +604,9 @@
   </si>
   <si>
     <t xml:space="preserve">The four age brackets add up to On hand. Over 60 days = 61 days or more. Avg age = tonnage-weighted average across all plants; Oldest batch = oldest at any plant (shaded by bracket).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last produced = the latest production date of the SKU at any plant, including a plant that holds none of it now.</t>
   </si>
   <si>
     <t xml:space="preserve">Hyderabad is the plant the Inventory Snapshot shows as Nippon. Hyderabad and Lepakshi serve South distributors; NPMD and Tapi serve West.</t>
@@ -1439,11 +1442,11 @@
       </c>
       <c r="C6" s="8" t="n">
         <f aca="false">SUMIF('SKU-wise'!$B$5:$B$130,A6,'SKU-wise'!$E$5:$E$130)</f>
-        <v>1410.286556828</v>
+        <v>1471.334939228</v>
       </c>
       <c r="D6" s="10" t="n">
         <f aca="false">SUMIF('SKU-wise'!$B$5:$B$130,A6,'SKU-wise'!$F$5:$F$130)</f>
-        <v>1165.019889792</v>
+        <v>1226.068272192</v>
       </c>
       <c r="E6" s="10" t="n">
         <f aca="false">SUMIF('SKU-wise'!$B$5:$B$130,A6,'SKU-wise'!$G$5:$G$130)</f>
@@ -1463,11 +1466,11 @@
       </c>
       <c r="I6" s="11" t="n">
         <f aca="false">IF(C6&gt;0,H6/C6,0)</f>
-        <v>0.0326430812441011</v>
+        <v>0.0312886599948173</v>
       </c>
       <c r="J6" s="12" t="n">
         <f aca="false">IF(C6&gt;0,SUMPRODUCT(('SKU-wise'!$B$5:$B$130=A6)*'SKU-wise'!$E$5:$E$130*'SKU-wise'!$L$5:$L$130)/C6,0)</f>
-        <v>24.5805155595196</v>
+        <v>23.6021167648699</v>
       </c>
       <c r="K6" s="10" t="n">
         <f aca="false">SUMIF('SKU-wise'!$B$5:$B$130,A6,'SKU-wise'!$O$5:$O$130)</f>
@@ -1483,7 +1486,7 @@
       </c>
       <c r="N6" s="10" t="n">
         <f aca="false">SUMIF('SKU-wise'!$B$5:$B$130,A6,'SKU-wise'!$R$5:$R$130)</f>
-        <v>378.0433036</v>
+        <v>439.091686</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1496,11 +1499,11 @@
       </c>
       <c r="C7" s="8" t="n">
         <f aca="false">SUMIF('SKU-wise'!$B$5:$B$130,A7,'SKU-wise'!$E$5:$E$130)</f>
-        <v>1016.934214764</v>
+        <v>1031.233774764</v>
       </c>
       <c r="D7" s="10" t="n">
         <f aca="false">SUMIF('SKU-wise'!$B$5:$B$130,A7,'SKU-wise'!$F$5:$F$130)</f>
-        <v>774.961075116001</v>
+        <v>789.260635116001</v>
       </c>
       <c r="E7" s="10" t="n">
         <f aca="false">SUMIF('SKU-wise'!$B$5:$B$130,A7,'SKU-wise'!$G$5:$G$130)</f>
@@ -1520,11 +1523,11 @@
       </c>
       <c r="I7" s="11" t="n">
         <f aca="false">IF(C7&gt;0,H7/C7,0)</f>
-        <v>0.0251642469143776</v>
+        <v>0.0248153079371905</v>
       </c>
       <c r="J7" s="12" t="n">
         <f aca="false">IF(C7&gt;0,SUMPRODUCT(('SKU-wise'!$B$5:$B$130=A7)*'SKU-wise'!$E$5:$E$130*'SKU-wise'!$L$5:$L$130)/C7,0)</f>
-        <v>23.422500547129</v>
+        <v>23.1115798812528</v>
       </c>
       <c r="K7" s="10" t="n">
         <f aca="false">SUMIF('SKU-wise'!$B$5:$B$130,A7,'SKU-wise'!$O$5:$O$130)</f>
@@ -1540,7 +1543,7 @@
       </c>
       <c r="N7" s="10" t="n">
         <f aca="false">SUMIF('SKU-wise'!$B$5:$B$130,A7,'SKU-wise'!$R$5:$R$130)</f>
-        <v>364.1532577</v>
+        <v>378.4528177</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1553,11 +1556,11 @@
       </c>
       <c r="C8" s="15" t="n">
         <f aca="false">SUM(C5:C7)</f>
-        <v>2813.82306871384</v>
+        <v>2889.17101111384</v>
       </c>
       <c r="D8" s="15" t="n">
         <f aca="false">SUM(D5:D7)</f>
-        <v>2021.65412963058</v>
+        <v>2097.00207203058</v>
       </c>
       <c r="E8" s="15" t="n">
         <f aca="false">SUM(E5:E7)</f>
@@ -1577,11 +1580,11 @@
       </c>
       <c r="I8" s="16" t="n">
         <f aca="false">IF(C8&gt;0,H8/C8,0)</f>
-        <v>0.104747195586381</v>
+        <v>0.102015448095753</v>
       </c>
       <c r="J8" s="17" t="n">
         <f aca="false">IF(C8&gt;0,SUMPRODUCT(C5:C7,J5:J7)/C8,0)</f>
-        <v>31.0215908005722</v>
+        <v>30.2386447286033</v>
       </c>
       <c r="K8" s="15" t="n">
         <f aca="false">SUM(K5:K7)</f>
@@ -1597,7 +1600,7 @@
       </c>
       <c r="N8" s="15" t="n">
         <f aca="false">SUM(N5:N7)</f>
-        <v>742.1965613</v>
+        <v>817.5445037</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1621,7 +1624,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:S139"/>
+  <dimension ref="A1:S140"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
@@ -3035,20 +3038,20 @@
         <v>17</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="D26" s="22" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="E26" s="8" t="n">
         <f aca="false">SUM(F26:I26)</f>
-        <v>44.145204</v>
+        <v>45.282544</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>40.37355</v>
+        <v>44.560368</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>3.771654</v>
+        <v>0.722176000000005</v>
       </c>
       <c r="H26" s="10" t="n">
         <v>0</v>
@@ -3065,53 +3068,53 @@
         <v>0</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>14.8447169255351</v>
+        <v>1.54223949961822</v>
       </c>
       <c r="M26" s="23" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N26" s="24" t="n">
-        <v>46311</v>
+        <v>46323</v>
       </c>
       <c r="O26" s="10" t="n">
         <v>0</v>
       </c>
       <c r="P26" s="10" t="n">
-        <v>3.771654</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="10" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="10" t="n">
-        <v>40.37355</v>
+        <v>45.282544</v>
       </c>
       <c r="S26" s="9" t="n">
         <f aca="false">COUNTIF(O26:R26,"&gt;0")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D27" s="22" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="E27" s="8" t="n">
         <f aca="false">SUM(F27:I27)</f>
-        <v>41.1114816</v>
+        <v>44.145204</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>31.229184</v>
+        <v>40.37355</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>9.8822976</v>
+        <v>3.771654</v>
       </c>
       <c r="H27" s="10" t="n">
         <v>0</v>
@@ -3128,25 +3131,25 @@
         <v>0</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>9.93247550582074</v>
+        <v>14.8447169255351</v>
       </c>
       <c r="M27" s="23" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N27" s="24" t="n">
-        <v>46322</v>
+        <v>46311</v>
       </c>
       <c r="O27" s="10" t="n">
-        <v>9.8822976</v>
+        <v>0</v>
       </c>
       <c r="P27" s="10" t="n">
-        <v>0</v>
+        <v>3.771654</v>
       </c>
       <c r="Q27" s="10" t="n">
         <v>0</v>
       </c>
       <c r="R27" s="10" t="n">
-        <v>31.229184</v>
+        <v>40.37355</v>
       </c>
       <c r="S27" s="9" t="n">
         <f aca="false">COUNTIF(O27:R27,"&gt;0")</f>
@@ -3161,20 +3164,20 @@
         <v>18</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D28" s="22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E28" s="8" t="n">
         <f aca="false">SUM(F28:I28)</f>
-        <v>39.269488</v>
+        <v>41.1114816</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>23.950528</v>
+        <v>31.229184</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>15.31896</v>
+        <v>9.8822976</v>
       </c>
       <c r="H28" s="10" t="n">
         <v>0</v>
@@ -3191,25 +3194,25 @@
         <v>0</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>21.1425554618894</v>
+        <v>9.93247550582074</v>
       </c>
       <c r="M28" s="23" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N28" s="24" t="n">
-        <v>46313</v>
+        <v>46322</v>
       </c>
       <c r="O28" s="10" t="n">
-        <v>0</v>
+        <v>9.8822976</v>
       </c>
       <c r="P28" s="10" t="n">
-        <v>15.31896</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="10" t="n">
-        <v>23.950528</v>
+        <v>0</v>
       </c>
       <c r="R28" s="10" t="n">
-        <v>0</v>
+        <v>31.229184</v>
       </c>
       <c r="S28" s="9" t="n">
         <f aca="false">COUNTIF(O28:R28,"&gt;0")</f>
@@ -3218,26 +3221,26 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B29" s="21" t="s">
         <v>18</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D29" s="22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E29" s="8" t="n">
         <f aca="false">SUM(F29:I29)</f>
-        <v>37.4979664</v>
+        <v>39.269488</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>37.4979664</v>
+        <v>23.950528</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>0</v>
+        <v>15.31896</v>
       </c>
       <c r="H29" s="10" t="n">
         <v>0</v>
@@ -3254,25 +3257,25 @@
         <v>0</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>7.07872648795162</v>
-      </c>
-      <c r="M29" s="25" t="n">
-        <v>29</v>
+        <v>21.1425554618894</v>
+      </c>
+      <c r="M29" s="23" t="n">
+        <v>37</v>
       </c>
       <c r="N29" s="24" t="n">
-        <v>46321</v>
+        <v>46316</v>
       </c>
       <c r="O29" s="10" t="n">
         <v>0</v>
       </c>
       <c r="P29" s="10" t="n">
-        <v>35.024976</v>
+        <v>15.31896</v>
       </c>
       <c r="Q29" s="10" t="n">
-        <v>0</v>
+        <v>23.950528</v>
       </c>
       <c r="R29" s="10" t="n">
-        <v>2.47299039999999</v>
+        <v>0</v>
       </c>
       <c r="S29" s="9" t="n">
         <f aca="false">COUNTIF(O29:R29,"&gt;0")</f>
@@ -3281,23 +3284,23 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B30" s="21" t="s">
         <v>18</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D30" s="22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E30" s="8" t="n">
         <f aca="false">SUM(F30:I30)</f>
-        <v>37.045768</v>
+        <v>37.4979664</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>37.045768</v>
+        <v>37.4979664</v>
       </c>
       <c r="G30" s="10" t="n">
         <v>0</v>
@@ -3317,29 +3320,29 @@
         <v>0</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>7.70206423578531</v>
+        <v>7.07872648795162</v>
       </c>
       <c r="M30" s="25" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="N30" s="24" t="n">
-        <v>46323</v>
+        <v>46321</v>
       </c>
       <c r="O30" s="10" t="n">
-        <v>37.045768</v>
+        <v>0</v>
       </c>
       <c r="P30" s="10" t="n">
-        <v>0</v>
+        <v>35.024976</v>
       </c>
       <c r="Q30" s="10" t="n">
         <v>0</v>
       </c>
       <c r="R30" s="10" t="n">
-        <v>0</v>
+        <v>2.47299039999999</v>
       </c>
       <c r="S30" s="9" t="n">
         <f aca="false">COUNTIF(O30:R30,"&gt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3347,20 +3350,20 @@
         <v>65</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C31" s="21" t="s">
         <v>66</v>
       </c>
       <c r="D31" s="22" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E31" s="8" t="n">
         <f aca="false">SUM(F31:I31)</f>
-        <v>34.3465701717689</v>
+        <v>37.045768</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>4.442621675858</v>
+        <v>37.045768</v>
       </c>
       <c r="G31" s="10" t="n">
         <v>0</v>
@@ -3369,27 +3372,27 @@
         <v>0</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>29.9039484959109</v>
-      </c>
-      <c r="J31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="10" t="n">
         <f aca="false">H31+I31</f>
-        <v>29.9039484959109</v>
+        <v>0</v>
       </c>
       <c r="K31" s="11" t="n">
         <f aca="false">IF(E31&gt;0,J31/E31,0)</f>
-        <v>0.870653120423954</v>
+        <v>0</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>94.8138563805834</v>
-      </c>
-      <c r="M31" s="28" t="n">
-        <v>114</v>
+        <v>7.70206423578531</v>
+      </c>
+      <c r="M31" s="25" t="n">
+        <v>23</v>
       </c>
       <c r="N31" s="24" t="n">
-        <v>46312</v>
+        <v>46323</v>
       </c>
       <c r="O31" s="10" t="n">
-        <v>34.3465701717689</v>
+        <v>37.045768</v>
       </c>
       <c r="P31" s="10" t="n">
         <v>0</v>
@@ -3416,14 +3419,14 @@
         <v>68</v>
       </c>
       <c r="D32" s="22" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E32" s="8" t="n">
         <f aca="false">SUM(F32:I32)</f>
-        <v>32.8148270267837</v>
+        <v>34.3465701717689</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>0</v>
+        <v>4.442621675858</v>
       </c>
       <c r="G32" s="10" t="n">
         <v>0</v>
@@ -3432,27 +3435,27 @@
         <v>0</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>32.8148270267837</v>
+        <v>29.9039484959109</v>
       </c>
       <c r="J32" s="26" t="n">
         <f aca="false">H32+I32</f>
-        <v>32.8148270267837</v>
+        <v>29.9039484959109</v>
       </c>
       <c r="K32" s="11" t="n">
         <f aca="false">IF(E32&gt;0,J32/E32,0)</f>
-        <v>1</v>
+        <v>0.870653120423954</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>115.009698645807</v>
+        <v>94.8138563805834</v>
       </c>
       <c r="M32" s="28" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="N32" s="24" t="n">
-        <v>46227</v>
+        <v>46312</v>
       </c>
       <c r="O32" s="10" t="n">
-        <v>32.8148270267837</v>
+        <v>34.3465701717689</v>
       </c>
       <c r="P32" s="10" t="n">
         <v>0</v>
@@ -3473,62 +3476,62 @@
         <v>69</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C33" s="21" t="s">
         <v>70</v>
       </c>
       <c r="D33" s="22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" s="8" t="n">
         <f aca="false">SUM(F33:I33)</f>
-        <v>30.9021872</v>
+        <v>32.8148270267837</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>30.3663824</v>
+        <v>0</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>0.535804799999998</v>
+        <v>0</v>
       </c>
       <c r="H33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="10" t="n">
+        <v>32.8148270267837</v>
+      </c>
+      <c r="J33" s="26" t="n">
         <f aca="false">H33+I33</f>
-        <v>0</v>
+        <v>32.8148270267837</v>
       </c>
       <c r="K33" s="11" t="n">
         <f aca="false">IF(E33&gt;0,J33/E33,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>4.00222498166731</v>
-      </c>
-      <c r="M33" s="23" t="n">
-        <v>40</v>
+        <v>115.009698645807</v>
+      </c>
+      <c r="M33" s="28" t="n">
+        <v>128</v>
       </c>
       <c r="N33" s="24" t="n">
-        <v>46323</v>
+        <v>46227</v>
       </c>
       <c r="O33" s="10" t="n">
-        <v>0</v>
+        <v>32.8148270267837</v>
       </c>
       <c r="P33" s="10" t="n">
-        <v>0.535804799999998</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="R33" s="10" t="n">
-        <v>30.3663824</v>
+        <v>0</v>
       </c>
       <c r="S33" s="9" t="n">
         <f aca="false">COUNTIF(O33:R33,"&gt;0")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3536,23 +3539,23 @@
         <v>71</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="D34" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" s="8" t="n">
         <f aca="false">SUM(F34:I34)</f>
-        <v>30.45868</v>
+        <v>30.9021872</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>30.45868</v>
+        <v>30.3663824</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>0</v>
+        <v>0.535804799999998</v>
       </c>
       <c r="H34" s="10" t="n">
         <v>0</v>
@@ -3569,50 +3572,50 @@
         <v>0</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="M34" s="25" t="n">
-        <v>23</v>
+        <v>4.00222498166731</v>
+      </c>
+      <c r="M34" s="23" t="n">
+        <v>40</v>
       </c>
       <c r="N34" s="24" t="n">
-        <v>46301</v>
+        <v>46323</v>
       </c>
       <c r="O34" s="10" t="n">
         <v>0</v>
       </c>
       <c r="P34" s="10" t="n">
-        <v>30.45868</v>
+        <v>0.535804799999998</v>
       </c>
       <c r="Q34" s="10" t="n">
         <v>0</v>
       </c>
       <c r="R34" s="10" t="n">
-        <v>0</v>
+        <v>30.3663824</v>
       </c>
       <c r="S34" s="9" t="n">
         <f aca="false">COUNTIF(O34:R34,"&gt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="D35" s="22" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="E35" s="8" t="n">
         <f aca="false">SUM(F35:I35)</f>
-        <v>29.8355663919971</v>
+        <v>30.45868</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>4.29513356116937</v>
+        <v>30.45868</v>
       </c>
       <c r="G35" s="10" t="n">
         <v>0</v>
@@ -3621,30 +3624,30 @@
         <v>0</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>25.5404328308278</v>
-      </c>
-      <c r="J35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="10" t="n">
         <f aca="false">H35+I35</f>
-        <v>25.5404328308278</v>
+        <v>0</v>
       </c>
       <c r="K35" s="11" t="n">
         <f aca="false">IF(E35&gt;0,J35/E35,0)</f>
-        <v>0.856039818224418</v>
+        <v>0</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>97.7556632766464</v>
-      </c>
-      <c r="M35" s="28" t="n">
-        <v>111</v>
+        <v>23</v>
+      </c>
+      <c r="M35" s="25" t="n">
+        <v>23</v>
       </c>
       <c r="N35" s="24" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="O35" s="10" t="n">
-        <v>29.8355663919971</v>
+        <v>0</v>
       </c>
       <c r="P35" s="10" t="n">
-        <v>0</v>
+        <v>30.45868</v>
       </c>
       <c r="Q35" s="10" t="n">
         <v>0</v>
@@ -3662,125 +3665,125 @@
         <v>74</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D36" s="22" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E36" s="8" t="n">
         <f aca="false">SUM(F36:I36)</f>
-        <v>25.1631552</v>
+        <v>29.8355663919971</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>24.8301344</v>
+        <v>4.29513356116937</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>0.333020799999996</v>
+        <v>0</v>
       </c>
       <c r="H36" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="10" t="n">
+        <v>25.5404328308278</v>
+      </c>
+      <c r="J36" s="26" t="n">
         <f aca="false">H36+I36</f>
-        <v>0</v>
+        <v>25.5404328308278</v>
       </c>
       <c r="K36" s="11" t="n">
         <f aca="false">IF(E36&gt;0,J36/E36,0)</f>
-        <v>0</v>
+        <v>0.856039818224418</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>17.5293784461497</v>
-      </c>
-      <c r="M36" s="23" t="n">
-        <v>57</v>
+        <v>97.7556632766464</v>
+      </c>
+      <c r="M36" s="28" t="n">
+        <v>111</v>
       </c>
       <c r="N36" s="24" t="n">
-        <v>46307</v>
+        <v>46305</v>
       </c>
       <c r="O36" s="10" t="n">
-        <v>0</v>
+        <v>29.8355663919971</v>
       </c>
       <c r="P36" s="10" t="n">
-        <v>0.333020799999996</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="10" t="n">
         <v>0</v>
       </c>
       <c r="R36" s="10" t="n">
-        <v>24.8301344</v>
+        <v>0</v>
       </c>
       <c r="S36" s="9" t="n">
         <f aca="false">COUNTIF(O36:R36,"&gt;0")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D37" s="22" t="n">
         <v>2</v>
       </c>
       <c r="E37" s="8" t="n">
         <f aca="false">SUM(F37:I37)</f>
-        <v>24.6311525361491</v>
+        <v>25.1631552</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>0</v>
+        <v>24.8301344</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>20.5254921809988</v>
+        <v>0.333020799999996</v>
       </c>
       <c r="H37" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>4.10566035515037</v>
-      </c>
-      <c r="J37" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="10" t="n">
         <f aca="false">H37+I37</f>
-        <v>4.10566035515037</v>
+        <v>0</v>
       </c>
       <c r="K37" s="11" t="n">
         <f aca="false">IF(E37&gt;0,J37/E37,0)</f>
-        <v>0.166685677786487</v>
+        <v>0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>49.0012547339082</v>
-      </c>
-      <c r="M37" s="28" t="n">
-        <v>104</v>
+        <v>17.5293784461497</v>
+      </c>
+      <c r="M37" s="23" t="n">
+        <v>57</v>
       </c>
       <c r="N37" s="24" t="n">
-        <v>46286</v>
+        <v>46307</v>
       </c>
       <c r="O37" s="10" t="n">
-        <v>24.6311525361491</v>
+        <v>0</v>
       </c>
       <c r="P37" s="10" t="n">
-        <v>0</v>
+        <v>0.333020799999996</v>
       </c>
       <c r="Q37" s="10" t="n">
         <v>0</v>
       </c>
       <c r="R37" s="10" t="n">
-        <v>0</v>
+        <v>24.8301344</v>
       </c>
       <c r="S37" s="9" t="n">
         <f aca="false">COUNTIF(O37:R37,"&gt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3788,49 +3791,49 @@
         <v>77</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="D38" s="22" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="E38" s="8" t="n">
         <f aca="false">SUM(F38:I38)</f>
-        <v>23.918199616</v>
+        <v>24.6311525361491</v>
       </c>
       <c r="F38" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>23.918199616</v>
+        <v>20.5254921809988</v>
       </c>
       <c r="H38" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="10" t="n">
+        <v>4.10566035515037</v>
+      </c>
+      <c r="J38" s="26" t="n">
         <f aca="false">H38+I38</f>
-        <v>0</v>
+        <v>4.10566035515037</v>
       </c>
       <c r="K38" s="11" t="n">
         <f aca="false">IF(E38&gt;0,J38/E38,0)</f>
-        <v>0</v>
+        <v>0.166685677786487</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="M38" s="23" t="n">
-        <v>50</v>
+        <v>49.0012547339082</v>
+      </c>
+      <c r="M38" s="28" t="n">
+        <v>104</v>
       </c>
       <c r="N38" s="24" t="n">
-        <v>46274</v>
+        <v>46286</v>
       </c>
       <c r="O38" s="10" t="n">
-        <v>23.918199616</v>
+        <v>24.6311525361491</v>
       </c>
       <c r="P38" s="10" t="n">
         <v>0</v>
@@ -3848,26 +3851,26 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="D39" s="22" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="E39" s="8" t="n">
         <f aca="false">SUM(F39:I39)</f>
-        <v>23.196887</v>
+        <v>23.918199616</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>23.196887</v>
+        <v>0</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>0</v>
+        <v>23.918199616</v>
       </c>
       <c r="H39" s="10" t="n">
         <v>0</v>
@@ -3884,19 +3887,19 @@
         <v>0</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>22.3923081575558</v>
-      </c>
-      <c r="M39" s="25" t="n">
-        <v>23</v>
+        <v>50</v>
+      </c>
+      <c r="M39" s="23" t="n">
+        <v>50</v>
       </c>
       <c r="N39" s="24" t="n">
-        <v>46302</v>
+        <v>46274</v>
       </c>
       <c r="O39" s="10" t="n">
-        <v>0</v>
+        <v>23.918199616</v>
       </c>
       <c r="P39" s="10" t="n">
-        <v>23.196887</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="10" t="n">
         <v>0</v>
@@ -3911,26 +3914,26 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D40" s="22" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E40" s="8" t="n">
         <f aca="false">SUM(F40:I40)</f>
-        <v>23.161798</v>
+        <v>23.196887</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>20.131482</v>
+        <v>23.196887</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>3.03031600000001</v>
+        <v>0</v>
       </c>
       <c r="H40" s="10" t="n">
         <v>0</v>
@@ -3947,19 +3950,19 @@
         <v>0</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>6.97163510363057</v>
-      </c>
-      <c r="M40" s="23" t="n">
-        <v>40</v>
+        <v>22.3923081575558</v>
+      </c>
+      <c r="M40" s="25" t="n">
+        <v>23</v>
       </c>
       <c r="N40" s="24" t="n">
-        <v>46322</v>
+        <v>46302</v>
       </c>
       <c r="O40" s="10" t="n">
-        <v>23.161798</v>
+        <v>0</v>
       </c>
       <c r="P40" s="10" t="n">
-        <v>0</v>
+        <v>23.196887</v>
       </c>
       <c r="Q40" s="10" t="n">
         <v>0</v>
@@ -3974,26 +3977,26 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="D41" s="22" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E41" s="8" t="n">
         <f aca="false">SUM(F41:I41)</f>
-        <v>22.771162</v>
+        <v>23.161798</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>22.771162</v>
+        <v>20.131482</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>0</v>
+        <v>3.03031600000001</v>
       </c>
       <c r="H41" s="10" t="n">
         <v>0</v>
@@ -4010,19 +4013,19 @@
         <v>0</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>29.8198418684123</v>
-      </c>
-      <c r="M41" s="25" t="n">
-        <v>30</v>
+        <v>6.97163510363057</v>
+      </c>
+      <c r="M41" s="23" t="n">
+        <v>40</v>
       </c>
       <c r="N41" s="24" t="n">
-        <v>46295</v>
+        <v>46322</v>
       </c>
       <c r="O41" s="10" t="n">
-        <v>0</v>
+        <v>23.161798</v>
       </c>
       <c r="P41" s="10" t="n">
-        <v>22.771162</v>
+        <v>0</v>
       </c>
       <c r="Q41" s="10" t="n">
         <v>0</v>
@@ -4037,23 +4040,23 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D42" s="22" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="E42" s="8" t="n">
         <f aca="false">SUM(F42:I42)</f>
-        <v>22.624130496</v>
+        <v>23.10726</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>22.624130496</v>
+        <v>23.10726</v>
       </c>
       <c r="G42" s="10" t="n">
         <v>0</v>
@@ -4073,16 +4076,16 @@
         <v>0</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>18.1019527443235</v>
+        <v>1.38116591928251</v>
       </c>
       <c r="M42" s="25" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="N42" s="24" t="n">
-        <v>46307</v>
+        <v>46323</v>
       </c>
       <c r="O42" s="10" t="n">
-        <v>22.624130496</v>
+        <v>0</v>
       </c>
       <c r="P42" s="10" t="n">
         <v>0</v>
@@ -4091,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="R42" s="10" t="n">
-        <v>0</v>
+        <v>23.10726</v>
       </c>
       <c r="S42" s="9" t="n">
         <f aca="false">COUNTIF(O42:R42,"&gt;0")</f>
@@ -4100,23 +4103,23 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B43" s="21" t="s">
         <v>17</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D43" s="22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E43" s="8" t="n">
         <f aca="false">SUM(F43:I43)</f>
-        <v>22.5846756</v>
+        <v>22.771162</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>22.5846756</v>
+        <v>22.771162</v>
       </c>
       <c r="G43" s="10" t="n">
         <v>0</v>
@@ -4136,34 +4139,34 @@
         <v>0</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>20.5205808845003</v>
+        <v>29.8198418684123</v>
       </c>
       <c r="M43" s="25" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N43" s="24" t="n">
-        <v>46304</v>
+        <v>46295</v>
       </c>
       <c r="O43" s="10" t="n">
         <v>0</v>
       </c>
       <c r="P43" s="10" t="n">
-        <v>2.392126</v>
+        <v>22.771162</v>
       </c>
       <c r="Q43" s="10" t="n">
         <v>0</v>
       </c>
       <c r="R43" s="10" t="n">
-        <v>20.1925496</v>
+        <v>0</v>
       </c>
       <c r="S43" s="9" t="n">
         <f aca="false">COUNTIF(O43:R43,"&gt;0")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B44" s="21" t="s">
         <v>17</v>
@@ -4172,17 +4175,17 @@
         <v>35</v>
       </c>
       <c r="D44" s="22" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="E44" s="8" t="n">
         <f aca="false">SUM(F44:I44)</f>
-        <v>22.5479504</v>
+        <v>22.624130496</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>0</v>
+        <v>22.624130496</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>22.5479504</v>
+        <v>0</v>
       </c>
       <c r="H44" s="10" t="n">
         <v>0</v>
@@ -4199,22 +4202,22 @@
         <v>0</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>52.0574965962317</v>
-      </c>
-      <c r="M44" s="23" t="n">
-        <v>53</v>
+        <v>18.1019527443235</v>
+      </c>
+      <c r="M44" s="25" t="n">
+        <v>19</v>
       </c>
       <c r="N44" s="24" t="n">
-        <v>46272</v>
+        <v>46307</v>
       </c>
       <c r="O44" s="10" t="n">
-        <v>0</v>
+        <v>22.624130496</v>
       </c>
       <c r="P44" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Q44" s="10" t="n">
-        <v>22.5479504</v>
+        <v>0</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>0</v>
@@ -4226,26 +4229,26 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="D45" s="22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E45" s="8" t="n">
         <f aca="false">SUM(F45:I45)</f>
-        <v>22.16657</v>
+        <v>22.5846756</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>20.13525</v>
+        <v>22.5846756</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>2.03132</v>
+        <v>0</v>
       </c>
       <c r="H45" s="10" t="n">
         <v>0</v>
@@ -4262,25 +4265,25 @@
         <v>0</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>6.41418812202339</v>
-      </c>
-      <c r="M45" s="23" t="n">
-        <v>60</v>
+        <v>20.5205808845003</v>
+      </c>
+      <c r="M45" s="25" t="n">
+        <v>22</v>
       </c>
       <c r="N45" s="24" t="n">
-        <v>46321</v>
+        <v>46304</v>
       </c>
       <c r="O45" s="10" t="n">
         <v>0</v>
       </c>
       <c r="P45" s="10" t="n">
-        <v>2.00522</v>
+        <v>2.392126</v>
       </c>
       <c r="Q45" s="10" t="n">
         <v>0</v>
       </c>
       <c r="R45" s="10" t="n">
-        <v>20.16135</v>
+        <v>20.1925496</v>
       </c>
       <c r="S45" s="9" t="n">
         <f aca="false">COUNTIF(O45:R45,"&gt;0")</f>
@@ -4289,58 +4292,58 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D46" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E46" s="8" t="n">
         <f aca="false">SUM(F46:I46)</f>
-        <v>21.8961</v>
+        <v>22.5479504</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>19.7679</v>
+        <v>0</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>0</v>
+        <v>22.5479504</v>
       </c>
       <c r="H46" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>2.1282</v>
-      </c>
-      <c r="J46" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="10" t="n">
         <f aca="false">H46+I46</f>
-        <v>2.1282</v>
+        <v>0</v>
       </c>
       <c r="K46" s="11" t="n">
         <f aca="false">IF(E46&gt;0,J46/E46,0)</f>
-        <v>0.097195390960034</v>
+        <v>0</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>19.6784358858427</v>
-      </c>
-      <c r="M46" s="28" t="n">
-        <v>91</v>
+        <v>52.0574965962317</v>
+      </c>
+      <c r="M46" s="23" t="n">
+        <v>53</v>
       </c>
       <c r="N46" s="24" t="n">
-        <v>46312</v>
+        <v>46272</v>
       </c>
       <c r="O46" s="10" t="n">
-        <v>21.8961</v>
+        <v>0</v>
       </c>
       <c r="P46" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="10" t="n">
-        <v>0</v>
+        <v>22.5479504</v>
       </c>
       <c r="R46" s="10" t="n">
         <v>0</v>
@@ -4352,26 +4355,26 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D47" s="22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E47" s="8" t="n">
         <f aca="false">SUM(F47:I47)</f>
-        <v>21.6809284</v>
+        <v>22.16657</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>16.787382</v>
+        <v>20.13525</v>
       </c>
       <c r="G47" s="10" t="n">
-        <v>4.8935464</v>
+        <v>2.03132</v>
       </c>
       <c r="H47" s="10" t="n">
         <v>0</v>
@@ -4388,29 +4391,29 @@
         <v>0</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>13.7712225828853</v>
+        <v>6.41418812202339</v>
       </c>
       <c r="M47" s="23" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="N47" s="24" t="n">
-        <v>46317</v>
+        <v>46321</v>
       </c>
       <c r="O47" s="10" t="n">
-        <v>21.6809284</v>
+        <v>0</v>
       </c>
       <c r="P47" s="10" t="n">
-        <v>0</v>
+        <v>2.00522</v>
       </c>
       <c r="Q47" s="10" t="n">
         <v>0</v>
       </c>
       <c r="R47" s="10" t="n">
-        <v>0</v>
+        <v>20.16135</v>
       </c>
       <c r="S47" s="9" t="n">
         <f aca="false">COUNTIF(O47:R47,"&gt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4418,49 +4421,49 @@
         <v>88</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D48" s="22" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="E48" s="8" t="n">
         <f aca="false">SUM(F48:I48)</f>
-        <v>21.377012416</v>
+        <v>21.8961</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>0</v>
+        <v>19.7679</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>15.579142656</v>
+        <v>0</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>5.79786976000001</v>
+        <v>0</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>0</v>
+        <v>2.1282</v>
       </c>
       <c r="J48" s="26" t="n">
         <f aca="false">H48+I48</f>
-        <v>5.79786976000001</v>
+        <v>2.1282</v>
       </c>
       <c r="K48" s="11" t="n">
         <f aca="false">IF(E48&gt;0,J48/E48,0)</f>
-        <v>0.271219834052231</v>
+        <v>0.097195390960034</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>48.1365950215669</v>
-      </c>
-      <c r="M48" s="27" t="n">
-        <v>70</v>
+        <v>19.6784358858427</v>
+      </c>
+      <c r="M48" s="28" t="n">
+        <v>91</v>
       </c>
       <c r="N48" s="24" t="n">
-        <v>46284</v>
+        <v>46312</v>
       </c>
       <c r="O48" s="10" t="n">
-        <v>21.377012416</v>
+        <v>21.8961</v>
       </c>
       <c r="P48" s="10" t="n">
         <v>0</v>
@@ -4481,49 +4484,49 @@
         <v>89</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C49" s="21" t="s">
         <v>90</v>
       </c>
       <c r="D49" s="22" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E49" s="8" t="n">
         <f aca="false">SUM(F49:I49)</f>
-        <v>20.3448108030086</v>
+        <v>21.6809284</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>9.57167752634869</v>
+        <v>16.787382</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>0</v>
+        <v>4.8935464</v>
       </c>
       <c r="H49" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>10.7731332766599</v>
-      </c>
-      <c r="J49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="10" t="n">
         <f aca="false">H49+I49</f>
-        <v>10.7731332766599</v>
+        <v>0</v>
       </c>
       <c r="K49" s="11" t="n">
         <f aca="false">IF(E49&gt;0,J49/E49,0)</f>
-        <v>0.529527326696338</v>
+        <v>0</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>60.4212407890997</v>
-      </c>
-      <c r="M49" s="28" t="n">
-        <v>99</v>
+        <v>13.7712225828853</v>
+      </c>
+      <c r="M49" s="23" t="n">
+        <v>37</v>
       </c>
       <c r="N49" s="24" t="n">
-        <v>46307</v>
+        <v>46317</v>
       </c>
       <c r="O49" s="10" t="n">
-        <v>20.3448108030086</v>
+        <v>21.6809284</v>
       </c>
       <c r="P49" s="10" t="n">
         <v>0</v>
@@ -4544,49 +4547,49 @@
         <v>91</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="D50" s="22" t="n">
         <v>2.8</v>
       </c>
       <c r="E50" s="8" t="n">
         <f aca="false">SUM(F50:I50)</f>
-        <v>20.02434368</v>
+        <v>21.377012416</v>
       </c>
       <c r="F50" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G50" s="10" t="n">
-        <v>0</v>
+        <v>15.579142656</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>0</v>
+        <v>5.79786976000001</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>20.02434368</v>
+        <v>0</v>
       </c>
       <c r="J50" s="26" t="n">
         <f aca="false">H50+I50</f>
-        <v>20.02434368</v>
+        <v>5.79786976000001</v>
       </c>
       <c r="K50" s="11" t="n">
         <f aca="false">IF(E50&gt;0,J50/E50,0)</f>
-        <v>1</v>
+        <v>0.271219834052231</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>188.054990378591</v>
-      </c>
-      <c r="M50" s="28" t="n">
-        <v>189</v>
+        <v>48.1365950215669</v>
+      </c>
+      <c r="M50" s="27" t="n">
+        <v>70</v>
       </c>
       <c r="N50" s="24" t="n">
-        <v>46139</v>
+        <v>46284</v>
       </c>
       <c r="O50" s="10" t="n">
-        <v>20.02434368</v>
+        <v>21.377012416</v>
       </c>
       <c r="P50" s="10" t="n">
         <v>0</v>
@@ -4604,23 +4607,23 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="21" t="s">
         <v>93</v>
-      </c>
-      <c r="B51" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C51" s="21" t="s">
-        <v>39</v>
       </c>
       <c r="D51" s="22" t="n">
         <v>1.6</v>
       </c>
       <c r="E51" s="8" t="n">
         <f aca="false">SUM(F51:I51)</f>
-        <v>19.777918528</v>
+        <v>20.3448108030086</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>19.777918528</v>
+        <v>9.57167752634869</v>
       </c>
       <c r="G51" s="10" t="n">
         <v>0</v>
@@ -4629,33 +4632,33 @@
         <v>0</v>
       </c>
       <c r="I51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="10" t="n">
+        <v>10.7731332766599</v>
+      </c>
+      <c r="J51" s="26" t="n">
         <f aca="false">H51+I51</f>
-        <v>0</v>
+        <v>10.7731332766599</v>
       </c>
       <c r="K51" s="11" t="n">
         <f aca="false">IF(E51&gt;0,J51/E51,0)</f>
-        <v>0</v>
+        <v>0.529527326696338</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="M51" s="25" t="n">
-        <v>13</v>
+        <v>60.4212407890997</v>
+      </c>
+      <c r="M51" s="28" t="n">
+        <v>99</v>
       </c>
       <c r="N51" s="24" t="n">
-        <v>46311</v>
+        <v>46307</v>
       </c>
       <c r="O51" s="10" t="n">
-        <v>0</v>
+        <v>20.3448108030086</v>
       </c>
       <c r="P51" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Q51" s="10" t="n">
-        <v>19.777918528</v>
+        <v>0</v>
       </c>
       <c r="R51" s="10" t="n">
         <v>0</v>
@@ -4670,20 +4673,20 @@
         <v>94</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="D52" s="22" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="E52" s="8" t="n">
         <f aca="false">SUM(F52:I52)</f>
-        <v>18.0739322420628</v>
+        <v>20.02434368</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>18.0739322420628</v>
+        <v>0</v>
       </c>
       <c r="G52" s="10" t="n">
         <v>0</v>
@@ -4692,27 +4695,27 @@
         <v>0</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="10" t="n">
+        <v>20.02434368</v>
+      </c>
+      <c r="J52" s="26" t="n">
         <f aca="false">H52+I52</f>
-        <v>0</v>
+        <v>20.02434368</v>
       </c>
       <c r="K52" s="11" t="n">
         <f aca="false">IF(E52&gt;0,J52/E52,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="M52" s="25" t="n">
-        <v>6</v>
+        <v>188.054990378591</v>
+      </c>
+      <c r="M52" s="28" t="n">
+        <v>189</v>
       </c>
       <c r="N52" s="24" t="n">
-        <v>46318</v>
+        <v>46139</v>
       </c>
       <c r="O52" s="10" t="n">
-        <v>18.0739322420628</v>
+        <v>20.02434368</v>
       </c>
       <c r="P52" s="10" t="n">
         <v>0</v>
@@ -4730,23 +4733,23 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B53" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="D53" s="22" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="E53" s="8" t="n">
         <f aca="false">SUM(F53:I53)</f>
-        <v>16.9689453224326</v>
+        <v>19.777918528</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>0</v>
+        <v>19.777918528</v>
       </c>
       <c r="G53" s="10" t="n">
         <v>0</v>
@@ -4755,33 +4758,33 @@
         <v>0</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>16.9689453224326</v>
-      </c>
-      <c r="J53" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="10" t="n">
         <f aca="false">H53+I53</f>
-        <v>16.9689453224326</v>
+        <v>0</v>
       </c>
       <c r="K53" s="11" t="n">
         <f aca="false">IF(E53&gt;0,J53/E53,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>114</v>
-      </c>
-      <c r="M53" s="28" t="n">
-        <v>114</v>
+        <v>13</v>
+      </c>
+      <c r="M53" s="25" t="n">
+        <v>13</v>
       </c>
       <c r="N53" s="24" t="n">
-        <v>46210</v>
+        <v>46311</v>
       </c>
       <c r="O53" s="10" t="n">
-        <v>16.9689453224326</v>
+        <v>0</v>
       </c>
       <c r="P53" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Q53" s="10" t="n">
-        <v>0</v>
+        <v>19.777918528</v>
       </c>
       <c r="R53" s="10" t="n">
         <v>0</v>
@@ -4793,23 +4796,23 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B54" s="21" t="s">
         <v>16</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D54" s="22" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="E54" s="8" t="n">
         <f aca="false">SUM(F54:I54)</f>
-        <v>15.987</v>
+        <v>18.0739322420628</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>0</v>
+        <v>18.0739322420628</v>
       </c>
       <c r="G54" s="10" t="n">
         <v>0</v>
@@ -4818,27 +4821,27 @@
         <v>0</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>15.987</v>
-      </c>
-      <c r="J54" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="10" t="n">
         <f aca="false">H54+I54</f>
-        <v>15.987</v>
+        <v>0</v>
       </c>
       <c r="K54" s="11" t="n">
         <f aca="false">IF(E54&gt;0,J54/E54,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>128</v>
-      </c>
-      <c r="M54" s="28" t="n">
-        <v>128</v>
+        <v>6</v>
+      </c>
+      <c r="M54" s="25" t="n">
+        <v>6</v>
       </c>
       <c r="N54" s="24" t="n">
-        <v>46196</v>
+        <v>46318</v>
       </c>
       <c r="O54" s="10" t="n">
-        <v>15.987</v>
+        <v>18.0739322420628</v>
       </c>
       <c r="P54" s="10" t="n">
         <v>0</v>
@@ -4856,26 +4859,26 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B55" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D55" s="22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E55" s="8" t="n">
         <f aca="false">SUM(F55:I55)</f>
-        <v>15.92302</v>
+        <v>17.5263252</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>15.92302</v>
+        <v>16.4880144</v>
       </c>
       <c r="G55" s="10" t="n">
-        <v>0</v>
+        <v>1.0383108</v>
       </c>
       <c r="H55" s="10" t="n">
         <v>0</v>
@@ -4892,13 +4895,13 @@
         <v>0</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>29.2492642727322</v>
-      </c>
-      <c r="M55" s="25" t="n">
-        <v>30</v>
+        <v>3.0735024362095</v>
+      </c>
+      <c r="M55" s="23" t="n">
+        <v>36</v>
       </c>
       <c r="N55" s="24" t="n">
-        <v>46295</v>
+        <v>46323</v>
       </c>
       <c r="O55" s="10" t="n">
         <v>0</v>
@@ -4910,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="R55" s="10" t="n">
-        <v>15.92302</v>
+        <v>17.5263252</v>
       </c>
       <c r="S55" s="9" t="n">
         <f aca="false">COUNTIF(O55:R55,"&gt;0")</f>
@@ -4919,20 +4922,20 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B56" s="21" t="s">
         <v>16</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D56" s="22" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E56" s="8" t="n">
         <f aca="false">SUM(F56:I56)</f>
-        <v>15.21</v>
+        <v>16.9689453224326</v>
       </c>
       <c r="F56" s="10" t="n">
         <v>0</v>
@@ -4944,27 +4947,27 @@
         <v>0</v>
       </c>
       <c r="I56" s="10" t="n">
-        <v>15.21</v>
+        <v>16.9689453224326</v>
       </c>
       <c r="J56" s="26" t="n">
         <f aca="false">H56+I56</f>
-        <v>15.21</v>
+        <v>16.9689453224326</v>
       </c>
       <c r="K56" s="11" t="n">
         <f aca="false">IF(E56&gt;0,J56/E56,0)</f>
         <v>1</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M56" s="28" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N56" s="24" t="n">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="O56" s="10" t="n">
-        <v>15.21</v>
+        <v>16.9689453224326</v>
       </c>
       <c r="P56" s="10" t="n">
         <v>0</v>
@@ -4982,52 +4985,52 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B57" s="21" t="s">
         <v>16</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="D57" s="22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E57" s="8" t="n">
         <f aca="false">SUM(F57:I57)</f>
-        <v>15.1022607216639</v>
+        <v>15.987</v>
       </c>
       <c r="F57" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>15.1022607216639</v>
+        <v>0</v>
       </c>
       <c r="H57" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="10" t="n">
+        <v>15.987</v>
+      </c>
+      <c r="J57" s="26" t="n">
         <f aca="false">H57+I57</f>
-        <v>0</v>
+        <v>15.987</v>
       </c>
       <c r="K57" s="11" t="n">
         <f aca="false">IF(E57&gt;0,J57/E57,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="M57" s="23" t="n">
-        <v>45</v>
+        <v>128</v>
+      </c>
+      <c r="M57" s="28" t="n">
+        <v>128</v>
       </c>
       <c r="N57" s="24" t="n">
-        <v>46279</v>
+        <v>46196</v>
       </c>
       <c r="O57" s="10" t="n">
-        <v>15.1022607216639</v>
+        <v>15.987</v>
       </c>
       <c r="P57" s="10" t="n">
         <v>0</v>
@@ -5048,23 +5051,23 @@
         <v>101</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>102</v>
+        <v>33</v>
       </c>
       <c r="D58" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E58" s="8" t="n">
         <f aca="false">SUM(F58:I58)</f>
-        <v>14.6710672</v>
+        <v>15.92302</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>10.3265808</v>
+        <v>15.92302</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>4.34448640000001</v>
+        <v>0</v>
       </c>
       <c r="H58" s="10" t="n">
         <v>0</v>
@@ -5081,16 +5084,16 @@
         <v>0</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>18.3302703977799</v>
-      </c>
-      <c r="M58" s="23" t="n">
-        <v>31</v>
+        <v>29.2492642727322</v>
+      </c>
+      <c r="M58" s="25" t="n">
+        <v>30</v>
       </c>
       <c r="N58" s="24" t="n">
-        <v>46311</v>
+        <v>46295</v>
       </c>
       <c r="O58" s="10" t="n">
-        <v>14.6710672</v>
+        <v>0</v>
       </c>
       <c r="P58" s="10" t="n">
         <v>0</v>
@@ -5099,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="R58" s="10" t="n">
-        <v>0</v>
+        <v>15.92302</v>
       </c>
       <c r="S58" s="9" t="n">
         <f aca="false">COUNTIF(O58:R58,"&gt;0")</f>
@@ -5108,52 +5111,52 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B59" s="21" t="s">
         <v>16</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="D59" s="22" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="E59" s="8" t="n">
         <f aca="false">SUM(F59:I59)</f>
-        <v>14.6224114638618</v>
+        <v>15.21</v>
       </c>
       <c r="F59" s="10" t="n">
-        <v>7.8330948808808</v>
+        <v>0</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>6.78931658298102</v>
+        <v>0</v>
       </c>
       <c r="H59" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="10" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="J59" s="26" t="n">
         <f aca="false">H59+I59</f>
-        <v>0</v>
+        <v>15.21</v>
       </c>
       <c r="K59" s="11" t="n">
         <f aca="false">IF(E59&gt;0,J59/E59,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>27.8753174205</v>
-      </c>
-      <c r="M59" s="23" t="n">
-        <v>41</v>
+        <v>113</v>
+      </c>
+      <c r="M59" s="28" t="n">
+        <v>113</v>
       </c>
       <c r="N59" s="24" t="n">
-        <v>46308</v>
+        <v>46211</v>
       </c>
       <c r="O59" s="10" t="n">
-        <v>14.6224114638618</v>
+        <v>15.21</v>
       </c>
       <c r="P59" s="10" t="n">
         <v>0</v>
@@ -5171,52 +5174,52 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B60" s="21" t="s">
         <v>16</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="D60" s="22" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E60" s="8" t="n">
         <f aca="false">SUM(F60:I60)</f>
-        <v>14.0415575471577</v>
+        <v>15.1022607216639</v>
       </c>
       <c r="F60" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>0</v>
+        <v>15.1022607216639</v>
       </c>
       <c r="H60" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="10" t="n">
-        <v>14.0415575471577</v>
-      </c>
-      <c r="J60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="10" t="n">
         <f aca="false">H60+I60</f>
-        <v>14.0415575471577</v>
+        <v>0</v>
       </c>
       <c r="K60" s="11" t="n">
         <f aca="false">IF(E60&gt;0,J60/E60,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>111.358501640932</v>
-      </c>
-      <c r="M60" s="28" t="n">
-        <v>127</v>
+        <v>45</v>
+      </c>
+      <c r="M60" s="23" t="n">
+        <v>45</v>
       </c>
       <c r="N60" s="24" t="n">
-        <v>46221</v>
+        <v>46279</v>
       </c>
       <c r="O60" s="10" t="n">
-        <v>14.0415575471577</v>
+        <v>15.1022607216639</v>
       </c>
       <c r="P60" s="10" t="n">
         <v>0</v>
@@ -5237,23 +5240,23 @@
         <v>105</v>
       </c>
       <c r="B61" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="D61" s="22" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="E61" s="8" t="n">
         <f aca="false">SUM(F61:I61)</f>
-        <v>13.193</v>
+        <v>14.6710672</v>
       </c>
       <c r="F61" s="10" t="n">
-        <v>0</v>
+        <v>10.3265808</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>13.193</v>
+        <v>4.34448640000001</v>
       </c>
       <c r="H61" s="10" t="n">
         <v>0</v>
@@ -5270,16 +5273,16 @@
         <v>0</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>38</v>
+        <v>18.3302703977799</v>
       </c>
       <c r="M61" s="23" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="N61" s="24" t="n">
-        <v>46286</v>
+        <v>46311</v>
       </c>
       <c r="O61" s="10" t="n">
-        <v>13.193</v>
+        <v>14.6710672</v>
       </c>
       <c r="P61" s="10" t="n">
         <v>0</v>
@@ -5297,52 +5300,52 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B62" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D62" s="22" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="E62" s="8" t="n">
         <f aca="false">SUM(F62:I62)</f>
-        <v>12.385894656</v>
+        <v>14.6224114638618</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>11.33534976</v>
+        <v>7.8330948808808</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>0</v>
+        <v>6.78931658298102</v>
       </c>
       <c r="H62" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="10" t="n">
-        <v>1.050544896</v>
-      </c>
-      <c r="J62" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="10" t="n">
         <f aca="false">H62+I62</f>
-        <v>1.050544896</v>
+        <v>0</v>
       </c>
       <c r="K62" s="11" t="n">
         <f aca="false">IF(E62&gt;0,J62/E62,0)</f>
-        <v>0.0848178452326086</v>
+        <v>0</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>25.7718663445413</v>
-      </c>
-      <c r="M62" s="28" t="n">
-        <v>142</v>
+        <v>27.8753174205</v>
+      </c>
+      <c r="M62" s="23" t="n">
+        <v>41</v>
       </c>
       <c r="N62" s="24" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="O62" s="10" t="n">
-        <v>12.385894656</v>
+        <v>14.6224114638618</v>
       </c>
       <c r="P62" s="10" t="n">
         <v>0</v>
@@ -5363,20 +5366,20 @@
         <v>108</v>
       </c>
       <c r="B63" s="21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="D63" s="22" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E63" s="8" t="n">
         <f aca="false">SUM(F63:I63)</f>
-        <v>12.3127576</v>
+        <v>14.0415575471577</v>
       </c>
       <c r="F63" s="10" t="n">
-        <v>12.3127576</v>
+        <v>0</v>
       </c>
       <c r="G63" s="10" t="n">
         <v>0</v>
@@ -5385,27 +5388,27 @@
         <v>0</v>
       </c>
       <c r="I63" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="10" t="n">
+        <v>14.0415575471577</v>
+      </c>
+      <c r="J63" s="26" t="n">
         <f aca="false">H63+I63</f>
-        <v>0</v>
+        <v>14.0415575471577</v>
       </c>
       <c r="K63" s="11" t="n">
         <f aca="false">IF(E63&gt;0,J63/E63,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>11.4840348030566</v>
-      </c>
-      <c r="M63" s="25" t="n">
-        <v>28</v>
+        <v>111.358501640932</v>
+      </c>
+      <c r="M63" s="28" t="n">
+        <v>127</v>
       </c>
       <c r="N63" s="24" t="n">
-        <v>46315</v>
+        <v>46221</v>
       </c>
       <c r="O63" s="10" t="n">
-        <v>12.3127576</v>
+        <v>14.0415575471577</v>
       </c>
       <c r="P63" s="10" t="n">
         <v>0</v>
@@ -5423,26 +5426,26 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B64" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="D64" s="22" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="E64" s="8" t="n">
         <f aca="false">SUM(F64:I64)</f>
-        <v>10.6625504</v>
+        <v>13.193</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>10.6625504</v>
+        <v>0</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>0</v>
+        <v>13.193</v>
       </c>
       <c r="H64" s="10" t="n">
         <v>0</v>
@@ -5459,50 +5462,50 @@
         <v>0</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>17.3916505379426</v>
-      </c>
-      <c r="M64" s="25" t="n">
-        <v>30</v>
+        <v>38</v>
+      </c>
+      <c r="M64" s="23" t="n">
+        <v>38</v>
       </c>
       <c r="N64" s="24" t="n">
-        <v>46315</v>
+        <v>46286</v>
       </c>
       <c r="O64" s="10" t="n">
-        <v>0</v>
+        <v>13.193</v>
       </c>
       <c r="P64" s="10" t="n">
-        <v>4.2607808</v>
+        <v>0</v>
       </c>
       <c r="Q64" s="10" t="n">
         <v>0</v>
       </c>
       <c r="R64" s="10" t="n">
-        <v>6.40176960000001</v>
+        <v>0</v>
       </c>
       <c r="S64" s="9" t="n">
         <f aca="false">COUNTIF(O64:R64,"&gt;0")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B65" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C65" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="B65" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" s="21" t="s">
-        <v>90</v>
-      </c>
       <c r="D65" s="22" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="E65" s="8" t="n">
         <f aca="false">SUM(F65:I65)</f>
-        <v>10.6181676337717</v>
+        <v>12.385894656</v>
       </c>
       <c r="F65" s="10" t="n">
-        <v>7.74440225389874</v>
+        <v>11.33534976</v>
       </c>
       <c r="G65" s="10" t="n">
         <v>0</v>
@@ -5511,27 +5514,27 @@
         <v>0</v>
       </c>
       <c r="I65" s="10" t="n">
-        <v>2.87376537987296</v>
+        <v>1.050544896</v>
       </c>
       <c r="J65" s="26" t="n">
         <f aca="false">H65+I65</f>
-        <v>2.87376537987296</v>
+        <v>1.050544896</v>
       </c>
       <c r="K65" s="11" t="n">
         <f aca="false">IF(E65&gt;0,J65/E65,0)</f>
-        <v>0.27064607369098</v>
+        <v>0.0848178452326086</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>38.4636241163514</v>
+        <v>25.7718663445413</v>
       </c>
       <c r="M65" s="28" t="n">
-        <v>99</v>
+        <v>142</v>
       </c>
       <c r="N65" s="24" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="O65" s="10" t="n">
-        <v>10.6181676337717</v>
+        <v>12.385894656</v>
       </c>
       <c r="P65" s="10" t="n">
         <v>0</v>
@@ -5555,20 +5558,20 @@
         <v>18</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="D66" s="22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E66" s="8" t="n">
         <f aca="false">SUM(F66:I66)</f>
-        <v>10.471432</v>
+        <v>12.3127576</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>0</v>
+        <v>12.3127576</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>10.471432</v>
+        <v>0</v>
       </c>
       <c r="H66" s="10" t="n">
         <v>0</v>
@@ -5585,16 +5588,16 @@
         <v>0</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>35.5627037066182</v>
-      </c>
-      <c r="M66" s="23" t="n">
-        <v>36</v>
+        <v>11.4840348030566</v>
+      </c>
+      <c r="M66" s="25" t="n">
+        <v>28</v>
       </c>
       <c r="N66" s="24" t="n">
-        <v>46289</v>
+        <v>46315</v>
       </c>
       <c r="O66" s="10" t="n">
-        <v>5.8923136</v>
+        <v>12.3127576</v>
       </c>
       <c r="P66" s="10" t="n">
         <v>0</v>
@@ -5603,32 +5606,32 @@
         <v>0</v>
       </c>
       <c r="R66" s="10" t="n">
-        <v>4.5791184</v>
+        <v>0</v>
       </c>
       <c r="S66" s="9" t="n">
         <f aca="false">COUNTIF(O66:R66,"&gt;0")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B67" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="D67" s="22" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="E67" s="8" t="n">
         <f aca="false">SUM(F67:I67)</f>
-        <v>9.9489</v>
+        <v>10.6625504</v>
       </c>
       <c r="F67" s="10" t="n">
-        <v>3.1789</v>
+        <v>10.6625504</v>
       </c>
       <c r="G67" s="10" t="n">
         <v>0</v>
@@ -5637,61 +5640,61 @@
         <v>0</v>
       </c>
       <c r="I67" s="10" t="n">
-        <v>6.77</v>
-      </c>
-      <c r="J67" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="10" t="n">
         <f aca="false">H67+I67</f>
-        <v>6.77</v>
+        <v>0</v>
       </c>
       <c r="K67" s="11" t="n">
         <f aca="false">IF(E67&gt;0,J67/E67,0)</f>
-        <v>0.680477238689704</v>
+        <v>0</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>65.7577018564866</v>
-      </c>
-      <c r="M67" s="28" t="n">
-        <v>91</v>
+        <v>17.3916505379426</v>
+      </c>
+      <c r="M67" s="25" t="n">
+        <v>30</v>
       </c>
       <c r="N67" s="24" t="n">
-        <v>46312</v>
+        <v>46315</v>
       </c>
       <c r="O67" s="10" t="n">
-        <v>9.9489</v>
+        <v>0</v>
       </c>
       <c r="P67" s="10" t="n">
-        <v>0</v>
+        <v>4.2607808</v>
       </c>
       <c r="Q67" s="10" t="n">
         <v>0</v>
       </c>
       <c r="R67" s="10" t="n">
-        <v>0</v>
+        <v>6.40176960000001</v>
       </c>
       <c r="S67" s="9" t="n">
         <f aca="false">COUNTIF(O67:R67,"&gt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="20" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B68" s="21" t="s">
         <v>16</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D68" s="22" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="E68" s="8" t="n">
         <f aca="false">SUM(F68:I68)</f>
-        <v>9.69094282016051</v>
+        <v>10.6181676337717</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>1.29804337827394</v>
+        <v>7.74440225389874</v>
       </c>
       <c r="G68" s="10" t="n">
         <v>0</v>
@@ -5700,27 +5703,27 @@
         <v>0</v>
       </c>
       <c r="I68" s="10" t="n">
-        <v>8.39289944188657</v>
+        <v>2.87376537987296</v>
       </c>
       <c r="J68" s="26" t="n">
         <f aca="false">H68+I68</f>
-        <v>8.39289944188657</v>
+        <v>2.87376537987296</v>
       </c>
       <c r="K68" s="11" t="n">
         <f aca="false">IF(E68&gt;0,J68/E68,0)</f>
-        <v>0.86605602753392</v>
+        <v>0.27064607369098</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>119.92672330407</v>
+        <v>38.4636241163514</v>
       </c>
       <c r="M68" s="28" t="n">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="N68" s="24" t="n">
         <v>46308</v>
       </c>
       <c r="O68" s="10" t="n">
-        <v>9.69094282016051</v>
+        <v>10.6181676337717</v>
       </c>
       <c r="P68" s="10" t="n">
         <v>0</v>
@@ -5738,26 +5741,26 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B69" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="D69" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E69" s="8" t="n">
         <f aca="false">SUM(F69:I69)</f>
-        <v>9.6667086</v>
+        <v>10.471432</v>
       </c>
       <c r="F69" s="10" t="n">
-        <v>6.1211178</v>
+        <v>0</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>3.5455908</v>
+        <v>10.471432</v>
       </c>
       <c r="H69" s="10" t="n">
         <v>0</v>
@@ -5774,25 +5777,25 @@
         <v>0</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>22.8685386254428</v>
+        <v>35.5627037066182</v>
       </c>
       <c r="M69" s="23" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N69" s="24" t="n">
-        <v>46307</v>
+        <v>46289</v>
       </c>
       <c r="O69" s="10" t="n">
-        <v>0</v>
+        <v>5.8923136</v>
       </c>
       <c r="P69" s="10" t="n">
-        <v>6.1211178</v>
+        <v>0</v>
       </c>
       <c r="Q69" s="10" t="n">
-        <v>3.5455908</v>
+        <v>0</v>
       </c>
       <c r="R69" s="10" t="n">
-        <v>0</v>
+        <v>4.5791184</v>
       </c>
       <c r="S69" s="9" t="n">
         <f aca="false">COUNTIF(O69:R69,"&gt;0")</f>
@@ -5801,23 +5804,23 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B70" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="D70" s="22" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="E70" s="8" t="n">
         <f aca="false">SUM(F70:I70)</f>
-        <v>9.59333920000001</v>
+        <v>9.9489</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>0</v>
+        <v>3.1789</v>
       </c>
       <c r="G70" s="10" t="n">
         <v>0</v>
@@ -5826,27 +5829,27 @@
         <v>0</v>
       </c>
       <c r="I70" s="10" t="n">
-        <v>9.59333920000001</v>
+        <v>6.77</v>
       </c>
       <c r="J70" s="26" t="n">
         <f aca="false">H70+I70</f>
-        <v>9.59333920000001</v>
+        <v>6.77</v>
       </c>
       <c r="K70" s="11" t="n">
         <f aca="false">IF(E70&gt;0,J70/E70,0)</f>
-        <v>1</v>
+        <v>0.680477238689704</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>187</v>
+        <v>65.7577018564866</v>
       </c>
       <c r="M70" s="28" t="n">
-        <v>187</v>
+        <v>91</v>
       </c>
       <c r="N70" s="24" t="n">
-        <v>46137</v>
+        <v>46312</v>
       </c>
       <c r="O70" s="10" t="n">
-        <v>9.59333920000001</v>
+        <v>9.9489</v>
       </c>
       <c r="P70" s="10" t="n">
         <v>0</v>
@@ -5864,52 +5867,52 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B71" s="21" t="s">
         <v>16</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D71" s="22" t="n">
         <v>2.8</v>
       </c>
       <c r="E71" s="8" t="n">
         <f aca="false">SUM(F71:I71)</f>
-        <v>9.48384355438487</v>
+        <v>9.69094282016051</v>
       </c>
       <c r="F71" s="10" t="n">
-        <v>0</v>
+        <v>1.29804337827394</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>9.48384355438487</v>
+        <v>0</v>
       </c>
       <c r="H71" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I71" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="10" t="n">
+        <v>8.39289944188657</v>
+      </c>
+      <c r="J71" s="26" t="n">
         <f aca="false">H71+I71</f>
-        <v>0</v>
+        <v>8.39289944188657</v>
       </c>
       <c r="K71" s="11" t="n">
         <f aca="false">IF(E71&gt;0,J71/E71,0)</f>
-        <v>0</v>
+        <v>0.86605602753392</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="M71" s="23" t="n">
-        <v>45</v>
+        <v>119.92672330407</v>
+      </c>
+      <c r="M71" s="28" t="n">
+        <v>136</v>
       </c>
       <c r="N71" s="24" t="n">
-        <v>46279</v>
+        <v>46308</v>
       </c>
       <c r="O71" s="10" t="n">
-        <v>9.48384355438487</v>
+        <v>9.69094282016051</v>
       </c>
       <c r="P71" s="10" t="n">
         <v>0</v>
@@ -5927,26 +5930,26 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="20" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B72" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="D72" s="22" t="n">
         <v>3</v>
       </c>
       <c r="E72" s="8" t="n">
         <f aca="false">SUM(F72:I72)</f>
-        <v>9.36337599999999</v>
+        <v>9.6667086</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>0</v>
+        <v>6.1211178</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>9.36337599999999</v>
+        <v>3.5455908</v>
       </c>
       <c r="H72" s="10" t="n">
         <v>0</v>
@@ -5963,47 +5966,47 @@
         <v>0</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>32</v>
+        <v>22.8685386254428</v>
       </c>
       <c r="M72" s="23" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N72" s="24" t="n">
-        <v>46292</v>
+        <v>46307</v>
       </c>
       <c r="O72" s="10" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="10" t="n">
-        <v>0</v>
+        <v>6.1211178</v>
       </c>
       <c r="Q72" s="10" t="n">
-        <v>0</v>
+        <v>3.5455908</v>
       </c>
       <c r="R72" s="10" t="n">
-        <v>9.36337599999999</v>
+        <v>0</v>
       </c>
       <c r="S72" s="9" t="n">
         <f aca="false">COUNTIF(O72:R72,"&gt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B73" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C73" s="21" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="D73" s="22" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E73" s="8" t="n">
         <f aca="false">SUM(F73:I73)</f>
-        <v>9.04905037447167</v>
+        <v>9.59333920000001</v>
       </c>
       <c r="F73" s="10" t="n">
         <v>0</v>
@@ -6012,30 +6015,30 @@
         <v>0</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>9.04905037447167</v>
+        <v>0</v>
       </c>
       <c r="I73" s="10" t="n">
-        <v>0</v>
+        <v>9.59333920000001</v>
       </c>
       <c r="J73" s="26" t="n">
         <f aca="false">H73+I73</f>
-        <v>9.04905037447167</v>
+        <v>9.59333920000001</v>
       </c>
       <c r="K73" s="11" t="n">
         <f aca="false">IF(E73&gt;0,J73/E73,0)</f>
         <v>1</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="M73" s="27" t="n">
-        <v>68</v>
+        <v>187</v>
+      </c>
+      <c r="M73" s="28" t="n">
+        <v>187</v>
       </c>
       <c r="N73" s="24" t="n">
-        <v>46256</v>
+        <v>46137</v>
       </c>
       <c r="O73" s="10" t="n">
-        <v>9.04905037447167</v>
+        <v>9.59333920000001</v>
       </c>
       <c r="P73" s="10" t="n">
         <v>0</v>
@@ -6056,23 +6059,23 @@
         <v>121</v>
       </c>
       <c r="B74" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C74" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D74" s="22" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="E74" s="8" t="n">
         <f aca="false">SUM(F74:I74)</f>
-        <v>8.83271839999999</v>
+        <v>9.48384355438487</v>
       </c>
       <c r="F74" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>8.83271839999999</v>
+        <v>9.48384355438487</v>
       </c>
       <c r="H74" s="10" t="n">
         <v>0</v>
@@ -6089,16 +6092,16 @@
         <v>0</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="M74" s="23" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="N74" s="24" t="n">
-        <v>46287</v>
+        <v>46279</v>
       </c>
       <c r="O74" s="10" t="n">
-        <v>8.83271839999999</v>
+        <v>9.48384355438487</v>
       </c>
       <c r="P74" s="10" t="n">
         <v>0</v>
@@ -6122,20 +6125,20 @@
         <v>18</v>
       </c>
       <c r="C75" s="21" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="D75" s="22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E75" s="8" t="n">
         <f aca="false">SUM(F75:I75)</f>
-        <v>8.8077</v>
+        <v>9.36337599999999</v>
       </c>
       <c r="F75" s="10" t="n">
-        <v>8.8077</v>
+        <v>0</v>
       </c>
       <c r="G75" s="10" t="n">
-        <v>0</v>
+        <v>9.36337599999999</v>
       </c>
       <c r="H75" s="10" t="n">
         <v>0</v>
@@ -6152,13 +6155,13 @@
         <v>0</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M75" s="25" t="n">
-        <v>2</v>
+        <v>32</v>
+      </c>
+      <c r="M75" s="23" t="n">
+        <v>32</v>
       </c>
       <c r="N75" s="24" t="n">
-        <v>46322</v>
+        <v>46292</v>
       </c>
       <c r="O75" s="10" t="n">
         <v>0</v>
@@ -6170,7 +6173,7 @@
         <v>0</v>
       </c>
       <c r="R75" s="10" t="n">
-        <v>8.8077</v>
+        <v>9.36337599999999</v>
       </c>
       <c r="S75" s="9" t="n">
         <f aca="false">COUNTIF(O75:R75,"&gt;0")</f>
@@ -6182,49 +6185,49 @@
         <v>123</v>
       </c>
       <c r="B76" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="D76" s="22" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="E76" s="8" t="n">
         <f aca="false">SUM(F76:I76)</f>
-        <v>8.6096</v>
+        <v>9.04905037447167</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>8.6096</v>
+        <v>0</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>0</v>
+        <v>9.04905037447167</v>
       </c>
       <c r="I76" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="10" t="n">
+      <c r="J76" s="26" t="n">
         <f aca="false">H76+I76</f>
-        <v>0</v>
+        <v>9.04905037447167</v>
       </c>
       <c r="K76" s="11" t="n">
         <f aca="false">IF(E76&gt;0,J76/E76,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="M76" s="25" t="n">
-        <v>28</v>
+        <v>68</v>
+      </c>
+      <c r="M76" s="27" t="n">
+        <v>68</v>
       </c>
       <c r="N76" s="24" t="n">
-        <v>46296</v>
+        <v>46256</v>
       </c>
       <c r="O76" s="10" t="n">
-        <v>8.6096</v>
+        <v>9.04905037447167</v>
       </c>
       <c r="P76" s="10" t="n">
         <v>0</v>
@@ -6242,26 +6245,26 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="20" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B77" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D77" s="22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E77" s="8" t="n">
         <f aca="false">SUM(F77:I77)</f>
-        <v>8.564212</v>
+        <v>8.83271839999999</v>
       </c>
       <c r="F77" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>8.564212</v>
+        <v>8.83271839999999</v>
       </c>
       <c r="H77" s="10" t="n">
         <v>0</v>
@@ -6278,16 +6281,16 @@
         <v>0</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M77" s="23" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N77" s="24" t="n">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="O77" s="10" t="n">
-        <v>0</v>
+        <v>8.83271839999999</v>
       </c>
       <c r="P77" s="10" t="n">
         <v>0</v>
@@ -6296,7 +6299,7 @@
         <v>0</v>
       </c>
       <c r="R77" s="10" t="n">
-        <v>8.564212</v>
+        <v>0</v>
       </c>
       <c r="S77" s="9" t="n">
         <f aca="false">COUNTIF(O77:R77,"&gt;0")</f>
@@ -6308,49 +6311,49 @@
         <v>126</v>
       </c>
       <c r="B78" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="D78" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E78" s="8" t="n">
         <f aca="false">SUM(F78:I78)</f>
-        <v>7.39196666203889</v>
+        <v>8.6096</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>0</v>
+        <v>8.6096</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>7.39196666203889</v>
+        <v>0</v>
       </c>
       <c r="I78" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J78" s="26" t="n">
+      <c r="J78" s="10" t="n">
         <f aca="false">H78+I78</f>
-        <v>7.39196666203889</v>
+        <v>0</v>
       </c>
       <c r="K78" s="11" t="n">
         <f aca="false">IF(E78&gt;0,J78/E78,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="M78" s="27" t="n">
-        <v>71</v>
+        <v>28</v>
+      </c>
+      <c r="M78" s="25" t="n">
+        <v>28</v>
       </c>
       <c r="N78" s="24" t="n">
-        <v>46253</v>
+        <v>46296</v>
       </c>
       <c r="O78" s="10" t="n">
-        <v>7.39196666203889</v>
+        <v>8.6096</v>
       </c>
       <c r="P78" s="10" t="n">
         <v>0</v>
@@ -6371,23 +6374,23 @@
         <v>127</v>
       </c>
       <c r="B79" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C79" s="21" t="s">
-        <v>31</v>
+        <v>128</v>
       </c>
       <c r="D79" s="22" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E79" s="8" t="n">
         <f aca="false">SUM(F79:I79)</f>
-        <v>7.15569465599997</v>
+        <v>8.564212</v>
       </c>
       <c r="F79" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>7.15569465599997</v>
+        <v>8.564212</v>
       </c>
       <c r="H79" s="10" t="n">
         <v>0</v>
@@ -6404,16 +6407,16 @@
         <v>0</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="M79" s="23" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="N79" s="24" t="n">
-        <v>46277</v>
+        <v>46290</v>
       </c>
       <c r="O79" s="10" t="n">
-        <v>7.15569465599997</v>
+        <v>0</v>
       </c>
       <c r="P79" s="10" t="n">
         <v>0</v>
@@ -6422,7 +6425,7 @@
         <v>0</v>
       </c>
       <c r="R79" s="10" t="n">
-        <v>0</v>
+        <v>8.564212</v>
       </c>
       <c r="S79" s="9" t="n">
         <f aca="false">COUNTIF(O79:R79,"&gt;0")</f>
@@ -6431,52 +6434,52 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="20" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B80" s="21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D80" s="22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E80" s="8" t="n">
         <f aca="false">SUM(F80:I80)</f>
-        <v>6.94151360000002</v>
+        <v>7.39196666203889</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>6.94151360000002</v>
+        <v>0</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>0</v>
+        <v>7.39196666203889</v>
       </c>
       <c r="I80" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J80" s="10" t="n">
+      <c r="J80" s="26" t="n">
         <f aca="false">H80+I80</f>
-        <v>0</v>
+        <v>7.39196666203889</v>
       </c>
       <c r="K80" s="11" t="n">
         <f aca="false">IF(E80&gt;0,J80/E80,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M80" s="25" t="n">
-        <v>3</v>
+        <v>71</v>
+      </c>
+      <c r="M80" s="27" t="n">
+        <v>71</v>
       </c>
       <c r="N80" s="24" t="n">
-        <v>46321</v>
+        <v>46253</v>
       </c>
       <c r="O80" s="10" t="n">
-        <v>0</v>
+        <v>7.39196666203889</v>
       </c>
       <c r="P80" s="10" t="n">
         <v>0</v>
@@ -6485,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="R80" s="10" t="n">
-        <v>6.94151360000002</v>
+        <v>0</v>
       </c>
       <c r="S80" s="9" t="n">
         <f aca="false">COUNTIF(O80:R80,"&gt;0")</f>
@@ -6494,52 +6497,52 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B81" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D81" s="22" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="E81" s="8" t="n">
         <f aca="false">SUM(F81:I81)</f>
-        <v>6.791192096</v>
+        <v>7.15569465599997</v>
       </c>
       <c r="F81" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G81" s="10" t="n">
-        <v>0</v>
+        <v>7.15569465599997</v>
       </c>
       <c r="H81" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I81" s="10" t="n">
-        <v>6.791192096</v>
-      </c>
-      <c r="J81" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="10" t="n">
         <f aca="false">H81+I81</f>
-        <v>6.791192096</v>
+        <v>0</v>
       </c>
       <c r="K81" s="11" t="n">
         <f aca="false">IF(E81&gt;0,J81/E81,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>211</v>
-      </c>
-      <c r="M81" s="28" t="n">
-        <v>211</v>
+        <v>47</v>
+      </c>
+      <c r="M81" s="23" t="n">
+        <v>47</v>
       </c>
       <c r="N81" s="24" t="n">
-        <v>46113</v>
+        <v>46277</v>
       </c>
       <c r="O81" s="10" t="n">
-        <v>6.791192096</v>
+        <v>7.15569465599997</v>
       </c>
       <c r="P81" s="10" t="n">
         <v>0</v>
@@ -6557,23 +6560,23 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B82" s="21" t="s">
         <v>18</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>131</v>
+        <v>72</v>
       </c>
       <c r="D82" s="22" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="E82" s="8" t="n">
         <f aca="false">SUM(F82:I82)</f>
-        <v>6.5123125</v>
+        <v>6.94151360000002</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>6.5123125</v>
+        <v>6.94151360000002</v>
       </c>
       <c r="G82" s="10" t="n">
         <v>0</v>
@@ -6593,25 +6596,25 @@
         <v>0</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="M82" s="25" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="N82" s="24" t="n">
-        <v>46305</v>
+        <v>46321</v>
       </c>
       <c r="O82" s="10" t="n">
         <v>0</v>
       </c>
       <c r="P82" s="10" t="n">
-        <v>6.5123125</v>
+        <v>0</v>
       </c>
       <c r="Q82" s="10" t="n">
         <v>0</v>
       </c>
       <c r="R82" s="10" t="n">
-        <v>0</v>
+        <v>6.94151360000002</v>
       </c>
       <c r="S82" s="9" t="n">
         <f aca="false">COUNTIF(O82:R82,"&gt;0")</f>
@@ -6623,17 +6626,17 @@
         <v>132</v>
       </c>
       <c r="B83" s="21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C83" s="21" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="E83" s="8" t="n">
         <f aca="false">SUM(F83:I83)</f>
-        <v>6.11666481737043</v>
+        <v>6.791192096</v>
       </c>
       <c r="F83" s="10" t="n">
         <v>0</v>
@@ -6645,27 +6648,27 @@
         <v>0</v>
       </c>
       <c r="I83" s="10" t="n">
-        <v>6.11666481737043</v>
+        <v>6.791192096</v>
       </c>
       <c r="J83" s="26" t="n">
         <f aca="false">H83+I83</f>
-        <v>6.11666481737043</v>
+        <v>6.791192096</v>
       </c>
       <c r="K83" s="11" t="n">
         <f aca="false">IF(E83&gt;0,J83/E83,0)</f>
         <v>1</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="M83" s="28" t="n">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="N83" s="24" t="n">
-        <v>46193</v>
+        <v>46113</v>
       </c>
       <c r="O83" s="10" t="n">
-        <v>6.11666481737043</v>
+        <v>6.791192096</v>
       </c>
       <c r="P83" s="10" t="n">
         <v>0</v>
@@ -6689,20 +6692,20 @@
         <v>18</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D84" s="22" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E84" s="8" t="n">
         <f aca="false">SUM(F84:I84)</f>
-        <v>5.66478880000001</v>
+        <v>6.5123125</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>5.55292480000001</v>
+        <v>6.5123125</v>
       </c>
       <c r="G84" s="10" t="n">
-        <v>0.111864</v>
+        <v>0</v>
       </c>
       <c r="H84" s="10" t="n">
         <v>0</v>
@@ -6719,10 +6722,10 @@
         <v>0</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>19.4146922476616</v>
-      </c>
-      <c r="M84" s="23" t="n">
-        <v>40</v>
+        <v>19</v>
+      </c>
+      <c r="M84" s="25" t="n">
+        <v>19</v>
       </c>
       <c r="N84" s="24" t="n">
         <v>46305</v>
@@ -6731,67 +6734,67 @@
         <v>0</v>
       </c>
       <c r="P84" s="10" t="n">
-        <v>5.55292480000001</v>
+        <v>6.5123125</v>
       </c>
       <c r="Q84" s="10" t="n">
         <v>0</v>
       </c>
       <c r="R84" s="10" t="n">
-        <v>0.111864</v>
+        <v>0</v>
       </c>
       <c r="S84" s="9" t="n">
         <f aca="false">COUNTIF(O84:R84,"&gt;0")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B85" s="21" t="s">
         <v>16</v>
       </c>
       <c r="C85" s="21" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="D85" s="22" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E85" s="8" t="n">
         <f aca="false">SUM(F85:I85)</f>
-        <v>5.4802</v>
+        <v>6.11666481737043</v>
       </c>
       <c r="F85" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G85" s="10" t="n">
-        <v>5.4802</v>
+        <v>0</v>
       </c>
       <c r="H85" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I85" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="10" t="n">
+        <v>6.11666481737043</v>
+      </c>
+      <c r="J85" s="26" t="n">
         <f aca="false">H85+I85</f>
-        <v>0</v>
+        <v>6.11666481737043</v>
       </c>
       <c r="K85" s="11" t="n">
         <f aca="false">IF(E85&gt;0,J85/E85,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="M85" s="23" t="n">
-        <v>33</v>
+        <v>131</v>
+      </c>
+      <c r="M85" s="28" t="n">
+        <v>131</v>
       </c>
       <c r="N85" s="24" t="n">
-        <v>46291</v>
+        <v>46193</v>
       </c>
       <c r="O85" s="10" t="n">
-        <v>5.4802</v>
+        <v>6.11666481737043</v>
       </c>
       <c r="P85" s="10" t="n">
         <v>0</v>
@@ -6812,62 +6815,62 @@
         <v>136</v>
       </c>
       <c r="B86" s="21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="D86" s="22" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E86" s="8" t="n">
         <f aca="false">SUM(F86:I86)</f>
-        <v>5.43362912409522</v>
+        <v>5.66478880000001</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>0</v>
+        <v>5.55292480000001</v>
       </c>
       <c r="G86" s="10" t="n">
-        <v>0</v>
+        <v>0.111864</v>
       </c>
       <c r="H86" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I86" s="10" t="n">
-        <v>5.43362912409522</v>
-      </c>
-      <c r="J86" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="10" t="n">
         <f aca="false">H86+I86</f>
-        <v>5.43362912409522</v>
+        <v>0</v>
       </c>
       <c r="K86" s="11" t="n">
         <f aca="false">IF(E86&gt;0,J86/E86,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>123</v>
-      </c>
-      <c r="M86" s="28" t="n">
-        <v>123</v>
+        <v>19.4146922476616</v>
+      </c>
+      <c r="M86" s="23" t="n">
+        <v>40</v>
       </c>
       <c r="N86" s="24" t="n">
-        <v>46201</v>
+        <v>46305</v>
       </c>
       <c r="O86" s="10" t="n">
-        <v>5.43362912409522</v>
+        <v>0</v>
       </c>
       <c r="P86" s="10" t="n">
-        <v>0</v>
+        <v>5.55292480000001</v>
       </c>
       <c r="Q86" s="10" t="n">
         <v>0</v>
       </c>
       <c r="R86" s="10" t="n">
-        <v>0</v>
+        <v>0.111864</v>
       </c>
       <c r="S86" s="9" t="n">
         <f aca="false">COUNTIF(O86:R86,"&gt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6878,20 +6881,20 @@
         <v>16</v>
       </c>
       <c r="C87" s="21" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D87" s="22" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E87" s="8" t="n">
         <f aca="false">SUM(F87:I87)</f>
-        <v>5.2602</v>
+        <v>5.4802</v>
       </c>
       <c r="F87" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>5.2602</v>
+        <v>5.4802</v>
       </c>
       <c r="H87" s="10" t="n">
         <v>0</v>
@@ -6908,16 +6911,16 @@
         <v>0</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M87" s="23" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N87" s="24" t="n">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="O87" s="10" t="n">
-        <v>5.2602</v>
+        <v>5.4802</v>
       </c>
       <c r="P87" s="10" t="n">
         <v>0</v>
@@ -6935,23 +6938,23 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="20" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B88" s="21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C88" s="21" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="D88" s="22" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E88" s="8" t="n">
         <f aca="false">SUM(F88:I88)</f>
-        <v>5.0504</v>
+        <v>5.43362912409522</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>5.0504</v>
+        <v>0</v>
       </c>
       <c r="G88" s="10" t="n">
         <v>0</v>
@@ -6960,27 +6963,27 @@
         <v>0</v>
       </c>
       <c r="I88" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="10" t="n">
+        <v>5.43362912409522</v>
+      </c>
+      <c r="J88" s="26" t="n">
         <f aca="false">H88+I88</f>
-        <v>0</v>
+        <v>5.43362912409522</v>
       </c>
       <c r="K88" s="11" t="n">
         <f aca="false">IF(E88&gt;0,J88/E88,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M88" s="25" t="n">
-        <v>3</v>
+        <v>123</v>
+      </c>
+      <c r="M88" s="28" t="n">
+        <v>123</v>
       </c>
       <c r="N88" s="24" t="n">
-        <v>46321</v>
+        <v>46201</v>
       </c>
       <c r="O88" s="10" t="n">
-        <v>0</v>
+        <v>5.43362912409522</v>
       </c>
       <c r="P88" s="10" t="n">
         <v>0</v>
@@ -6989,7 +6992,7 @@
         <v>0</v>
       </c>
       <c r="R88" s="10" t="n">
-        <v>5.0504</v>
+        <v>0</v>
       </c>
       <c r="S88" s="9" t="n">
         <f aca="false">COUNTIF(O88:R88,"&gt;0")</f>
@@ -7001,23 +7004,23 @@
         <v>140</v>
       </c>
       <c r="B89" s="21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C89" s="21" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="D89" s="22" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="E89" s="8" t="n">
         <f aca="false">SUM(F89:I89)</f>
-        <v>4.754208</v>
+        <v>5.2602</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>4.667348</v>
+        <v>0</v>
       </c>
       <c r="G89" s="10" t="n">
-        <v>0.0868599999999997</v>
+        <v>5.2602</v>
       </c>
       <c r="H89" s="10" t="n">
         <v>0</v>
@@ -7034,29 +7037,29 @@
         <v>0</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>23.3105922164112</v>
+        <v>31</v>
       </c>
       <c r="M89" s="23" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="N89" s="24" t="n">
-        <v>46301</v>
+        <v>46293</v>
       </c>
       <c r="O89" s="10" t="n">
-        <v>0</v>
+        <v>5.2602</v>
       </c>
       <c r="P89" s="10" t="n">
-        <v>4.667348</v>
+        <v>0</v>
       </c>
       <c r="Q89" s="10" t="n">
         <v>0</v>
       </c>
       <c r="R89" s="10" t="n">
-        <v>0.0868599999999997</v>
+        <v>0</v>
       </c>
       <c r="S89" s="9" t="n">
         <f aca="false">COUNTIF(O89:R89,"&gt;0")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7064,23 +7067,23 @@
         <v>141</v>
       </c>
       <c r="B90" s="21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="D90" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E90" s="8" t="n">
         <f aca="false">SUM(F90:I90)</f>
-        <v>4.63078547616842</v>
+        <v>5.0504</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>0</v>
+        <v>5.0504</v>
       </c>
       <c r="G90" s="10" t="n">
-        <v>4.63078547616842</v>
+        <v>0</v>
       </c>
       <c r="H90" s="10" t="n">
         <v>0</v>
@@ -7097,16 +7100,16 @@
         <v>0</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="M90" s="23" t="n">
-        <v>52</v>
+        <v>3</v>
+      </c>
+      <c r="M90" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="N90" s="24" t="n">
-        <v>46272</v>
+        <v>46321</v>
       </c>
       <c r="O90" s="10" t="n">
-        <v>4.63078547616842</v>
+        <v>0</v>
       </c>
       <c r="P90" s="10" t="n">
         <v>0</v>
@@ -7115,7 +7118,7 @@
         <v>0</v>
       </c>
       <c r="R90" s="10" t="n">
-        <v>0</v>
+        <v>5.0504</v>
       </c>
       <c r="S90" s="9" t="n">
         <f aca="false">COUNTIF(O90:R90,"&gt;0")</f>
@@ -7124,89 +7127,89 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="20" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B91" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C91" s="21" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="D91" s="22" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E91" s="8" t="n">
         <f aca="false">SUM(F91:I91)</f>
-        <v>4.38852</v>
+        <v>4.754208</v>
       </c>
       <c r="F91" s="10" t="n">
-        <v>0</v>
+        <v>4.667348</v>
       </c>
       <c r="G91" s="10" t="n">
-        <v>2.390325</v>
+        <v>0.0868599999999997</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>1.998195</v>
+        <v>0</v>
       </c>
       <c r="I91" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J91" s="26" t="n">
+      <c r="J91" s="10" t="n">
         <f aca="false">H91+I91</f>
-        <v>1.998195</v>
+        <v>0</v>
       </c>
       <c r="K91" s="11" t="n">
         <f aca="false">IF(E91&gt;0,J91/E91,0)</f>
-        <v>0.455323206912582</v>
+        <v>0</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>53.3916354488529</v>
-      </c>
-      <c r="M91" s="27" t="n">
-        <v>73</v>
+        <v>23.3105922164112</v>
+      </c>
+      <c r="M91" s="23" t="n">
+        <v>40</v>
       </c>
       <c r="N91" s="24" t="n">
-        <v>46287</v>
+        <v>46301</v>
       </c>
       <c r="O91" s="10" t="n">
-        <v>4.38852</v>
+        <v>0</v>
       </c>
       <c r="P91" s="10" t="n">
-        <v>0</v>
+        <v>4.667348</v>
       </c>
       <c r="Q91" s="10" t="n">
         <v>0</v>
       </c>
       <c r="R91" s="10" t="n">
-        <v>0</v>
+        <v>0.0868599999999997</v>
       </c>
       <c r="S91" s="9" t="n">
         <f aca="false">COUNTIF(O91:R91,"&gt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B92" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C92" s="21" t="s">
-        <v>144</v>
+        <v>75</v>
       </c>
       <c r="D92" s="22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E92" s="8" t="n">
         <f aca="false">SUM(F92:I92)</f>
-        <v>3.9753</v>
+        <v>4.63078547616842</v>
       </c>
       <c r="F92" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G92" s="10" t="n">
-        <v>3.9753</v>
+        <v>4.63078547616842</v>
       </c>
       <c r="H92" s="10" t="n">
         <v>0</v>
@@ -7223,16 +7226,16 @@
         <v>0</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M92" s="23" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="N92" s="24" t="n">
-        <v>46287</v>
+        <v>46272</v>
       </c>
       <c r="O92" s="10" t="n">
-        <v>0</v>
+        <v>4.63078547616842</v>
       </c>
       <c r="P92" s="10" t="n">
         <v>0</v>
@@ -7241,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="R92" s="10" t="n">
-        <v>3.9753</v>
+        <v>0</v>
       </c>
       <c r="S92" s="9" t="n">
         <f aca="false">COUNTIF(O92:R92,"&gt;0")</f>
@@ -7256,46 +7259,46 @@
         <v>17</v>
       </c>
       <c r="C93" s="21" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="D93" s="22" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="E93" s="8" t="n">
         <f aca="false">SUM(F93:I93)</f>
-        <v>3.8724</v>
+        <v>4.38852</v>
       </c>
       <c r="F93" s="10" t="n">
-        <v>3.8724</v>
+        <v>0</v>
       </c>
       <c r="G93" s="10" t="n">
-        <v>0</v>
+        <v>2.390325</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>0</v>
+        <v>1.998195</v>
       </c>
       <c r="I93" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J93" s="10" t="n">
+      <c r="J93" s="26" t="n">
         <f aca="false">H93+I93</f>
-        <v>0</v>
+        <v>1.998195</v>
       </c>
       <c r="K93" s="11" t="n">
         <f aca="false">IF(E93&gt;0,J93/E93,0)</f>
-        <v>0</v>
+        <v>0.455323206912582</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="M93" s="25" t="n">
-        <v>27</v>
+        <v>53.3916354488529</v>
+      </c>
+      <c r="M93" s="27" t="n">
+        <v>73</v>
       </c>
       <c r="N93" s="24" t="n">
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="O93" s="10" t="n">
-        <v>0</v>
+        <v>4.38852</v>
       </c>
       <c r="P93" s="10" t="n">
         <v>0</v>
@@ -7304,7 +7307,7 @@
         <v>0</v>
       </c>
       <c r="R93" s="10" t="n">
-        <v>3.8724</v>
+        <v>0</v>
       </c>
       <c r="S93" s="9" t="n">
         <f aca="false">COUNTIF(O93:R93,"&gt;0")</f>
@@ -7319,46 +7322,46 @@
         <v>17</v>
       </c>
       <c r="C94" s="21" t="s">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="D94" s="22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E94" s="8" t="n">
         <f aca="false">SUM(F94:I94)</f>
-        <v>3.7845792</v>
+        <v>3.9753</v>
       </c>
       <c r="F94" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G94" s="10" t="n">
-        <v>0</v>
+        <v>3.9753</v>
       </c>
       <c r="H94" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I94" s="10" t="n">
-        <v>3.7845792</v>
-      </c>
-      <c r="J94" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="10" t="n">
         <f aca="false">H94+I94</f>
-        <v>3.7845792</v>
+        <v>0</v>
       </c>
       <c r="K94" s="11" t="n">
         <f aca="false">IF(E94&gt;0,J94/E94,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>141</v>
-      </c>
-      <c r="M94" s="28" t="n">
-        <v>141</v>
+        <v>37</v>
+      </c>
+      <c r="M94" s="23" t="n">
+        <v>37</v>
       </c>
       <c r="N94" s="24" t="n">
-        <v>46183</v>
+        <v>46287</v>
       </c>
       <c r="O94" s="10" t="n">
-        <v>3.7845792</v>
+        <v>0</v>
       </c>
       <c r="P94" s="10" t="n">
         <v>0</v>
@@ -7367,7 +7370,7 @@
         <v>0</v>
       </c>
       <c r="R94" s="10" t="n">
-        <v>0</v>
+        <v>3.9753</v>
       </c>
       <c r="S94" s="9" t="n">
         <f aca="false">COUNTIF(O94:R94,"&gt;0")</f>
@@ -7376,23 +7379,23 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="20" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B95" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C95" s="21" t="s">
-        <v>148</v>
+        <v>35</v>
       </c>
       <c r="D95" s="22" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="E95" s="8" t="n">
         <f aca="false">SUM(F95:I95)</f>
-        <v>3.4545625</v>
+        <v>3.8724</v>
       </c>
       <c r="F95" s="10" t="n">
-        <v>1.0232475</v>
+        <v>3.8724</v>
       </c>
       <c r="G95" s="10" t="n">
         <v>0</v>
@@ -7401,27 +7404,27 @@
         <v>0</v>
       </c>
       <c r="I95" s="10" t="n">
-        <v>2.431315</v>
-      </c>
-      <c r="J95" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="10" t="n">
         <f aca="false">H95+I95</f>
-        <v>2.431315</v>
+        <v>0</v>
       </c>
       <c r="K95" s="11" t="n">
         <f aca="false">IF(E95&gt;0,J95/E95,0)</f>
-        <v>0.703798237837642</v>
+        <v>0</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>85.0836220216019</v>
-      </c>
-      <c r="M95" s="28" t="n">
-        <v>115</v>
+        <v>27</v>
+      </c>
+      <c r="M95" s="25" t="n">
+        <v>27</v>
       </c>
       <c r="N95" s="24" t="n">
-        <v>46310</v>
+        <v>46297</v>
       </c>
       <c r="O95" s="10" t="n">
-        <v>3.4545625</v>
+        <v>0</v>
       </c>
       <c r="P95" s="10" t="n">
         <v>0</v>
@@ -7430,7 +7433,7 @@
         <v>0</v>
       </c>
       <c r="R95" s="10" t="n">
-        <v>0</v>
+        <v>3.8724</v>
       </c>
       <c r="S95" s="9" t="n">
         <f aca="false">COUNTIF(O95:R95,"&gt;0")</f>
@@ -7442,49 +7445,49 @@
         <v>149</v>
       </c>
       <c r="B96" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D96" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E96" s="8" t="n">
         <f aca="false">SUM(F96:I96)</f>
-        <v>3.413064</v>
+        <v>3.7845792</v>
       </c>
       <c r="F96" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G96" s="10" t="n">
-        <v>3.413064</v>
+        <v>0</v>
       </c>
       <c r="H96" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I96" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="10" t="n">
+        <v>3.7845792</v>
+      </c>
+      <c r="J96" s="26" t="n">
         <f aca="false">H96+I96</f>
-        <v>0</v>
+        <v>3.7845792</v>
       </c>
       <c r="K96" s="11" t="n">
         <f aca="false">IF(E96&gt;0,J96/E96,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="M96" s="23" t="n">
-        <v>34</v>
+        <v>141</v>
+      </c>
+      <c r="M96" s="28" t="n">
+        <v>141</v>
       </c>
       <c r="N96" s="24" t="n">
-        <v>46290</v>
+        <v>46183</v>
       </c>
       <c r="O96" s="10" t="n">
-        <v>0</v>
+        <v>3.7845792</v>
       </c>
       <c r="P96" s="10" t="n">
         <v>0</v>
@@ -7493,7 +7496,7 @@
         <v>0</v>
       </c>
       <c r="R96" s="10" t="n">
-        <v>3.413064</v>
+        <v>0</v>
       </c>
       <c r="S96" s="9" t="n">
         <f aca="false">COUNTIF(O96:R96,"&gt;0")</f>
@@ -7505,20 +7508,20 @@
         <v>150</v>
       </c>
       <c r="B97" s="21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C97" s="21" t="s">
-        <v>66</v>
+        <v>151</v>
       </c>
       <c r="D97" s="22" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="E97" s="8" t="n">
         <f aca="false">SUM(F97:I97)</f>
-        <v>3.41136734497612</v>
+        <v>3.4545625</v>
       </c>
       <c r="F97" s="10" t="n">
-        <v>0</v>
+        <v>1.0232475</v>
       </c>
       <c r="G97" s="10" t="n">
         <v>0</v>
@@ -7527,27 +7530,27 @@
         <v>0</v>
       </c>
       <c r="I97" s="10" t="n">
-        <v>3.41136734497612</v>
+        <v>2.431315</v>
       </c>
       <c r="J97" s="26" t="n">
         <f aca="false">H97+I97</f>
-        <v>3.41136734497612</v>
+        <v>2.431315</v>
       </c>
       <c r="K97" s="11" t="n">
         <f aca="false">IF(E97&gt;0,J97/E97,0)</f>
-        <v>1</v>
+        <v>0.703798237837642</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>113</v>
+        <v>85.0836220216019</v>
       </c>
       <c r="M97" s="28" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="N97" s="24" t="n">
-        <v>46211</v>
+        <v>46310</v>
       </c>
       <c r="O97" s="10" t="n">
-        <v>3.41136734497612</v>
+        <v>3.4545625</v>
       </c>
       <c r="P97" s="10" t="n">
         <v>0</v>
@@ -7565,52 +7568,52 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B98" s="21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D98" s="22" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="E98" s="8" t="n">
         <f aca="false">SUM(F98:I98)</f>
-        <v>3.40154390180969</v>
+        <v>3.413064</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>3.10468585141395</v>
+        <v>0</v>
       </c>
       <c r="G98" s="10" t="n">
-        <v>0</v>
+        <v>3.413064</v>
       </c>
       <c r="H98" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I98" s="10" t="n">
-        <v>0.296858050395738</v>
-      </c>
-      <c r="J98" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="10" t="n">
         <f aca="false">H98+I98</f>
-        <v>0.296858050395738</v>
+        <v>0</v>
       </c>
       <c r="K98" s="11" t="n">
         <f aca="false">IF(E98&gt;0,J98/E98,0)</f>
-        <v>0.0872715622567162</v>
+        <v>0</v>
       </c>
       <c r="L98" s="12" t="n">
-        <v>34.1162552898746</v>
-      </c>
-      <c r="M98" s="28" t="n">
-        <v>119</v>
+        <v>34</v>
+      </c>
+      <c r="M98" s="23" t="n">
+        <v>34</v>
       </c>
       <c r="N98" s="24" t="n">
-        <v>46298</v>
+        <v>46290</v>
       </c>
       <c r="O98" s="10" t="n">
-        <v>3.40154390180969</v>
+        <v>0</v>
       </c>
       <c r="P98" s="10" t="n">
         <v>0</v>
@@ -7619,7 +7622,7 @@
         <v>0</v>
       </c>
       <c r="R98" s="10" t="n">
-        <v>0</v>
+        <v>3.413064</v>
       </c>
       <c r="S98" s="9" t="n">
         <f aca="false">COUNTIF(O98:R98,"&gt;0")</f>
@@ -7628,7 +7631,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="20" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B99" s="21" t="s">
         <v>16</v>
@@ -7641,7 +7644,7 @@
       </c>
       <c r="E99" s="8" t="n">
         <f aca="false">SUM(F99:I99)</f>
-        <v>3.32262312468675</v>
+        <v>3.41136734497612</v>
       </c>
       <c r="F99" s="10" t="n">
         <v>0</v>
@@ -7653,27 +7656,27 @@
         <v>0</v>
       </c>
       <c r="I99" s="10" t="n">
-        <v>3.32262312468675</v>
+        <v>3.41136734497612</v>
       </c>
       <c r="J99" s="26" t="n">
         <f aca="false">H99+I99</f>
-        <v>3.32262312468675</v>
+        <v>3.41136734497612</v>
       </c>
       <c r="K99" s="11" t="n">
         <f aca="false">IF(E99&gt;0,J99/E99,0)</f>
         <v>1</v>
       </c>
       <c r="L99" s="12" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="M99" s="28" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="N99" s="24" t="n">
-        <v>46221</v>
+        <v>46211</v>
       </c>
       <c r="O99" s="10" t="n">
-        <v>3.32262312468675</v>
+        <v>3.41136734497612</v>
       </c>
       <c r="P99" s="10" t="n">
         <v>0</v>
@@ -7691,23 +7694,23 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B100" s="21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="D100" s="22" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="E100" s="8" t="n">
         <f aca="false">SUM(F100:I100)</f>
-        <v>3.2119</v>
+        <v>3.40154390180969</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>3.2119</v>
+        <v>3.10468585141395</v>
       </c>
       <c r="G100" s="10" t="n">
         <v>0</v>
@@ -7716,27 +7719,27 @@
         <v>0</v>
       </c>
       <c r="I100" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="10" t="n">
+        <v>0.296858050395738</v>
+      </c>
+      <c r="J100" s="26" t="n">
         <f aca="false">H100+I100</f>
-        <v>0</v>
+        <v>0.296858050395738</v>
       </c>
       <c r="K100" s="11" t="n">
         <f aca="false">IF(E100&gt;0,J100/E100,0)</f>
-        <v>0</v>
+        <v>0.0872715622567162</v>
       </c>
       <c r="L100" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="M100" s="25" t="n">
-        <v>26</v>
+        <v>34.1162552898746</v>
+      </c>
+      <c r="M100" s="28" t="n">
+        <v>119</v>
       </c>
       <c r="N100" s="24" t="n">
         <v>46298</v>
       </c>
       <c r="O100" s="10" t="n">
-        <v>3.2119</v>
+        <v>3.40154390180969</v>
       </c>
       <c r="P100" s="10" t="n">
         <v>0</v>
@@ -7754,52 +7757,52 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B101" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C101" s="21" t="s">
-        <v>144</v>
+        <v>70</v>
       </c>
       <c r="D101" s="22" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="E101" s="8" t="n">
         <f aca="false">SUM(F101:I101)</f>
-        <v>3.092136</v>
+        <v>3.32262312468675</v>
       </c>
       <c r="F101" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G101" s="10" t="n">
-        <v>3.092136</v>
+        <v>0</v>
       </c>
       <c r="H101" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I101" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="10" t="n">
+        <v>3.32262312468675</v>
+      </c>
+      <c r="J101" s="26" t="n">
         <f aca="false">H101+I101</f>
-        <v>0</v>
+        <v>3.32262312468675</v>
       </c>
       <c r="K101" s="11" t="n">
         <f aca="false">IF(E101&gt;0,J101/E101,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="M101" s="23" t="n">
-        <v>38</v>
+        <v>103</v>
+      </c>
+      <c r="M101" s="28" t="n">
+        <v>103</v>
       </c>
       <c r="N101" s="24" t="n">
-        <v>46286</v>
+        <v>46221</v>
       </c>
       <c r="O101" s="10" t="n">
-        <v>0</v>
+        <v>3.32262312468675</v>
       </c>
       <c r="P101" s="10" t="n">
         <v>0</v>
@@ -7808,7 +7811,7 @@
         <v>0</v>
       </c>
       <c r="R101" s="10" t="n">
-        <v>3.092136</v>
+        <v>0</v>
       </c>
       <c r="S101" s="9" t="n">
         <f aca="false">COUNTIF(O101:R101,"&gt;0")</f>
@@ -7817,52 +7820,52 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="20" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B102" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="D102" s="22" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="E102" s="8" t="n">
         <f aca="false">SUM(F102:I102)</f>
-        <v>3.09150749999996</v>
+        <v>3.2119</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>0</v>
+        <v>3.2119</v>
       </c>
       <c r="G102" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H102" s="10" t="n">
-        <v>3.09150749999996</v>
+        <v>0</v>
       </c>
       <c r="I102" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J102" s="26" t="n">
+      <c r="J102" s="10" t="n">
         <f aca="false">H102+I102</f>
-        <v>3.09150749999996</v>
+        <v>0</v>
       </c>
       <c r="K102" s="11" t="n">
         <f aca="false">IF(E102&gt;0,J102/E102,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="M102" s="27" t="n">
-        <v>69</v>
+        <v>26</v>
+      </c>
+      <c r="M102" s="25" t="n">
+        <v>26</v>
       </c>
       <c r="N102" s="24" t="n">
-        <v>46255</v>
+        <v>46298</v>
       </c>
       <c r="O102" s="10" t="n">
-        <v>3.09150749999996</v>
+        <v>3.2119</v>
       </c>
       <c r="P102" s="10" t="n">
         <v>0</v>
@@ -7880,26 +7883,26 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B103" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C103" s="21" t="s">
-        <v>70</v>
+        <v>147</v>
       </c>
       <c r="D103" s="22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E103" s="8" t="n">
         <f aca="false">SUM(F103:I103)</f>
-        <v>2.66855360000001</v>
+        <v>3.092136</v>
       </c>
       <c r="F103" s="10" t="n">
-        <v>2.66855360000001</v>
+        <v>0</v>
       </c>
       <c r="G103" s="10" t="n">
-        <v>0</v>
+        <v>3.092136</v>
       </c>
       <c r="H103" s="10" t="n">
         <v>0</v>
@@ -7916,13 +7919,13 @@
         <v>0</v>
       </c>
       <c r="L103" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="M103" s="25" t="n">
-        <v>15</v>
+        <v>38</v>
+      </c>
+      <c r="M103" s="23" t="n">
+        <v>38</v>
       </c>
       <c r="N103" s="24" t="n">
-        <v>46309</v>
+        <v>46286</v>
       </c>
       <c r="O103" s="10" t="n">
         <v>0</v>
@@ -7934,7 +7937,7 @@
         <v>0</v>
       </c>
       <c r="R103" s="10" t="n">
-        <v>2.66855360000001</v>
+        <v>3.092136</v>
       </c>
       <c r="S103" s="9" t="n">
         <f aca="false">COUNTIF(O103:R103,"&gt;0")</f>
@@ -7943,20 +7946,20 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B104" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C104" s="21" t="s">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="D104" s="22" t="n">
         <v>2.5</v>
       </c>
       <c r="E104" s="8" t="n">
         <f aca="false">SUM(F104:I104)</f>
-        <v>2.4611925</v>
+        <v>3.09150749999996</v>
       </c>
       <c r="F104" s="10" t="n">
         <v>0</v>
@@ -7965,30 +7968,30 @@
         <v>0</v>
       </c>
       <c r="H104" s="10" t="n">
-        <v>0</v>
+        <v>3.09150749999996</v>
       </c>
       <c r="I104" s="10" t="n">
-        <v>2.4611925</v>
+        <v>0</v>
       </c>
       <c r="J104" s="26" t="n">
         <f aca="false">H104+I104</f>
-        <v>2.4611925</v>
+        <v>3.09150749999996</v>
       </c>
       <c r="K104" s="11" t="n">
         <f aca="false">IF(E104&gt;0,J104/E104,0)</f>
         <v>1</v>
       </c>
       <c r="L104" s="12" t="n">
-        <v>122</v>
-      </c>
-      <c r="M104" s="28" t="n">
-        <v>122</v>
+        <v>69</v>
+      </c>
+      <c r="M104" s="27" t="n">
+        <v>69</v>
       </c>
       <c r="N104" s="24" t="n">
-        <v>46202</v>
+        <v>46255</v>
       </c>
       <c r="O104" s="10" t="n">
-        <v>2.4611925</v>
+        <v>3.09150749999996</v>
       </c>
       <c r="P104" s="10" t="n">
         <v>0</v>
@@ -8006,23 +8009,23 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="20" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B105" s="21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C105" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D105" s="22" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="E105" s="8" t="n">
         <f aca="false">SUM(F105:I105)</f>
-        <v>2.36277335267008</v>
+        <v>2.66855360000001</v>
       </c>
       <c r="F105" s="10" t="n">
-        <v>2.36277335267008</v>
+        <v>2.66855360000001</v>
       </c>
       <c r="G105" s="10" t="n">
         <v>0</v>
@@ -8042,16 +8045,16 @@
         <v>0</v>
       </c>
       <c r="L105" s="12" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M105" s="25" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N105" s="24" t="n">
-        <v>46305</v>
+        <v>46309</v>
       </c>
       <c r="O105" s="10" t="n">
-        <v>2.36277335267008</v>
+        <v>0</v>
       </c>
       <c r="P105" s="10" t="n">
         <v>0</v>
@@ -8060,7 +8063,7 @@
         <v>0</v>
       </c>
       <c r="R105" s="10" t="n">
-        <v>0</v>
+        <v>2.66855360000001</v>
       </c>
       <c r="S105" s="9" t="n">
         <f aca="false">COUNTIF(O105:R105,"&gt;0")</f>
@@ -8069,58 +8072,58 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="20" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B106" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C106" s="21" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="D106" s="22" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="E106" s="8" t="n">
         <f aca="false">SUM(F106:I106)</f>
-        <v>2.153178688</v>
+        <v>2.4611925</v>
       </c>
       <c r="F106" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G106" s="10" t="n">
-        <v>2.153178688</v>
+        <v>0</v>
       </c>
       <c r="H106" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I106" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="10" t="n">
+        <v>2.4611925</v>
+      </c>
+      <c r="J106" s="26" t="n">
         <f aca="false">H106+I106</f>
-        <v>0</v>
+        <v>2.4611925</v>
       </c>
       <c r="K106" s="11" t="n">
         <f aca="false">IF(E106&gt;0,J106/E106,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="M106" s="23" t="n">
-        <v>36</v>
+        <v>122</v>
+      </c>
+      <c r="M106" s="28" t="n">
+        <v>122</v>
       </c>
       <c r="N106" s="24" t="n">
-        <v>46288</v>
+        <v>46202</v>
       </c>
       <c r="O106" s="10" t="n">
-        <v>0</v>
+        <v>2.4611925</v>
       </c>
       <c r="P106" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Q106" s="10" t="n">
-        <v>2.153178688</v>
+        <v>0</v>
       </c>
       <c r="R106" s="10" t="n">
         <v>0</v>
@@ -8132,23 +8135,23 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="20" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B107" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C107" s="21" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="D107" s="22" t="n">
         <v>2.8</v>
       </c>
       <c r="E107" s="8" t="n">
         <f aca="false">SUM(F107:I107)</f>
-        <v>2.06041052800003</v>
+        <v>2.36277335267008</v>
       </c>
       <c r="F107" s="10" t="n">
-        <v>0</v>
+        <v>2.36277335267008</v>
       </c>
       <c r="G107" s="10" t="n">
         <v>0</v>
@@ -8157,27 +8160,27 @@
         <v>0</v>
       </c>
       <c r="I107" s="10" t="n">
-        <v>2.06041052800003</v>
-      </c>
-      <c r="J107" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="10" t="n">
         <f aca="false">H107+I107</f>
-        <v>2.06041052800003</v>
+        <v>0</v>
       </c>
       <c r="K107" s="11" t="n">
         <f aca="false">IF(E107&gt;0,J107/E107,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="12" t="n">
-        <v>114</v>
-      </c>
-      <c r="M107" s="28" t="n">
-        <v>114</v>
+        <v>19</v>
+      </c>
+      <c r="M107" s="25" t="n">
+        <v>19</v>
       </c>
       <c r="N107" s="24" t="n">
-        <v>46210</v>
+        <v>46305</v>
       </c>
       <c r="O107" s="10" t="n">
-        <v>2.06041052800003</v>
+        <v>2.36277335267008</v>
       </c>
       <c r="P107" s="10" t="n">
         <v>0</v>
@@ -8195,58 +8198,58 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="20" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B108" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C108" s="21" t="s">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="D108" s="22" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="E108" s="8" t="n">
         <f aca="false">SUM(F108:I108)</f>
-        <v>1.978658352</v>
+        <v>2.153178688</v>
       </c>
       <c r="F108" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G108" s="10" t="n">
-        <v>0</v>
+        <v>2.153178688</v>
       </c>
       <c r="H108" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I108" s="10" t="n">
-        <v>1.978658352</v>
-      </c>
-      <c r="J108" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="10" t="n">
         <f aca="false">H108+I108</f>
-        <v>1.978658352</v>
+        <v>0</v>
       </c>
       <c r="K108" s="11" t="n">
         <f aca="false">IF(E108&gt;0,J108/E108,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="12" t="n">
-        <v>211</v>
-      </c>
-      <c r="M108" s="28" t="n">
-        <v>211</v>
+        <v>36</v>
+      </c>
+      <c r="M108" s="23" t="n">
+        <v>36</v>
       </c>
       <c r="N108" s="24" t="n">
-        <v>46113</v>
+        <v>46300</v>
       </c>
       <c r="O108" s="10" t="n">
-        <v>1.978658352</v>
+        <v>0</v>
       </c>
       <c r="P108" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Q108" s="10" t="n">
-        <v>0</v>
+        <v>2.153178688</v>
       </c>
       <c r="R108" s="10" t="n">
         <v>0</v>
@@ -8258,20 +8261,20 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="20" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B109" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C109" s="21" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="D109" s="22" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="E109" s="8" t="n">
         <f aca="false">SUM(F109:I109)</f>
-        <v>1.6796943760219</v>
+        <v>2.06041052800003</v>
       </c>
       <c r="F109" s="10" t="n">
         <v>0</v>
@@ -8283,27 +8286,27 @@
         <v>0</v>
       </c>
       <c r="I109" s="10" t="n">
-        <v>1.6796943760219</v>
+        <v>2.06041052800003</v>
       </c>
       <c r="J109" s="26" t="n">
         <f aca="false">H109+I109</f>
-        <v>1.6796943760219</v>
+        <v>2.06041052800003</v>
       </c>
       <c r="K109" s="11" t="n">
         <f aca="false">IF(E109&gt;0,J109/E109,0)</f>
         <v>1</v>
       </c>
       <c r="L109" s="12" t="n">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="M109" s="28" t="n">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="N109" s="24" t="n">
-        <v>46227</v>
+        <v>46210</v>
       </c>
       <c r="O109" s="10" t="n">
-        <v>1.6796943760219</v>
+        <v>2.06041052800003</v>
       </c>
       <c r="P109" s="10" t="n">
         <v>0</v>
@@ -8321,23 +8324,23 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="20" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B110" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C110" s="21" t="s">
-        <v>102</v>
+        <v>33</v>
       </c>
       <c r="D110" s="22" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E110" s="8" t="n">
         <f aca="false">SUM(F110:I110)</f>
-        <v>1.6739992</v>
+        <v>1.978658352</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>1.6739992</v>
+        <v>0</v>
       </c>
       <c r="G110" s="10" t="n">
         <v>0</v>
@@ -8346,27 +8349,27 @@
         <v>0</v>
       </c>
       <c r="I110" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" s="10" t="n">
+        <v>1.978658352</v>
+      </c>
+      <c r="J110" s="26" t="n">
         <f aca="false">H110+I110</f>
-        <v>0</v>
+        <v>1.978658352</v>
       </c>
       <c r="K110" s="11" t="n">
         <f aca="false">IF(E110&gt;0,J110/E110,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="M110" s="25" t="n">
-        <v>13</v>
+        <v>211</v>
+      </c>
+      <c r="M110" s="28" t="n">
+        <v>211</v>
       </c>
       <c r="N110" s="24" t="n">
-        <v>46311</v>
+        <v>46113</v>
       </c>
       <c r="O110" s="10" t="n">
-        <v>1.6739992</v>
+        <v>1.978658352</v>
       </c>
       <c r="P110" s="10" t="n">
         <v>0</v>
@@ -8384,20 +8387,20 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B111" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C111" s="21" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="D111" s="22" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="E111" s="8" t="n">
         <f aca="false">SUM(F111:I111)</f>
-        <v>1.66718272</v>
+        <v>1.6796943760219</v>
       </c>
       <c r="F111" s="10" t="n">
         <v>0</v>
@@ -8409,27 +8412,27 @@
         <v>0</v>
       </c>
       <c r="I111" s="10" t="n">
-        <v>1.66718272</v>
+        <v>1.6796943760219</v>
       </c>
       <c r="J111" s="26" t="n">
         <f aca="false">H111+I111</f>
-        <v>1.66718272</v>
+        <v>1.6796943760219</v>
       </c>
       <c r="K111" s="11" t="n">
         <f aca="false">IF(E111&gt;0,J111/E111,0)</f>
         <v>1</v>
       </c>
       <c r="L111" s="12" t="n">
-        <v>166</v>
+        <v>97</v>
       </c>
       <c r="M111" s="28" t="n">
-        <v>166</v>
+        <v>97</v>
       </c>
       <c r="N111" s="24" t="n">
-        <v>46158</v>
+        <v>46227</v>
       </c>
       <c r="O111" s="10" t="n">
-        <v>1.66718272</v>
+        <v>1.6796943760219</v>
       </c>
       <c r="P111" s="10" t="n">
         <v>0</v>
@@ -8447,23 +8450,23 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="20" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B112" s="21" t="s">
         <v>17</v>
       </c>
       <c r="C112" s="21" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="D112" s="22" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="E112" s="8" t="n">
         <f aca="false">SUM(F112:I112)</f>
-        <v>1.49284396800001</v>
+        <v>1.6739992</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>0</v>
+        <v>1.6739992</v>
       </c>
       <c r="G112" s="10" t="n">
         <v>0</v>
@@ -8472,27 +8475,27 @@
         <v>0</v>
       </c>
       <c r="I112" s="10" t="n">
-        <v>1.49284396800001</v>
-      </c>
-      <c r="J112" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="10" t="n">
         <f aca="false">H112+I112</f>
-        <v>1.49284396800001</v>
+        <v>0</v>
       </c>
       <c r="K112" s="11" t="n">
         <f aca="false">IF(E112&gt;0,J112/E112,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" s="12" t="n">
-        <v>162</v>
-      </c>
-      <c r="M112" s="28" t="n">
-        <v>162</v>
+        <v>13</v>
+      </c>
+      <c r="M112" s="25" t="n">
+        <v>13</v>
       </c>
       <c r="N112" s="24" t="n">
-        <v>46162</v>
+        <v>46311</v>
       </c>
       <c r="O112" s="10" t="n">
-        <v>1.49284396800001</v>
+        <v>1.6739992</v>
       </c>
       <c r="P112" s="10" t="n">
         <v>0</v>
@@ -8510,52 +8513,52 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="20" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B113" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C113" s="21" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="D113" s="22" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="E113" s="8" t="n">
         <f aca="false">SUM(F113:I113)</f>
-        <v>1.35044088702466</v>
+        <v>1.66718272</v>
       </c>
       <c r="F113" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G113" s="10" t="n">
-        <v>1.35044088702466</v>
+        <v>0</v>
       </c>
       <c r="H113" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I113" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" s="10" t="n">
+        <v>1.66718272</v>
+      </c>
+      <c r="J113" s="26" t="n">
         <f aca="false">H113+I113</f>
-        <v>0</v>
+        <v>1.66718272</v>
       </c>
       <c r="K113" s="11" t="n">
         <f aca="false">IF(E113&gt;0,J113/E113,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="M113" s="23" t="n">
-        <v>52</v>
+        <v>166</v>
+      </c>
+      <c r="M113" s="28" t="n">
+        <v>166</v>
       </c>
       <c r="N113" s="24" t="n">
-        <v>46272</v>
+        <v>46158</v>
       </c>
       <c r="O113" s="10" t="n">
-        <v>1.35044088702466</v>
+        <v>1.66718272</v>
       </c>
       <c r="P113" s="10" t="n">
         <v>0</v>
@@ -8573,23 +8576,23 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="20" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B114" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C114" s="21" t="s">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="D114" s="22" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="E114" s="8" t="n">
         <f aca="false">SUM(F114:I114)</f>
-        <v>1.29797439999999</v>
+        <v>1.49284396800001</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>1.29797439999999</v>
+        <v>0</v>
       </c>
       <c r="G114" s="10" t="n">
         <v>0</v>
@@ -8598,33 +8601,33 @@
         <v>0</v>
       </c>
       <c r="I114" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" s="10" t="n">
+        <v>1.49284396800001</v>
+      </c>
+      <c r="J114" s="26" t="n">
         <f aca="false">H114+I114</f>
-        <v>0</v>
+        <v>1.49284396800001</v>
       </c>
       <c r="K114" s="11" t="n">
         <f aca="false">IF(E114&gt;0,J114/E114,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="M114" s="25" t="n">
-        <v>27</v>
+        <v>162</v>
+      </c>
+      <c r="M114" s="28" t="n">
+        <v>162</v>
       </c>
       <c r="N114" s="24" t="n">
-        <v>46297</v>
+        <v>46162</v>
       </c>
       <c r="O114" s="10" t="n">
-        <v>0</v>
+        <v>1.49284396800001</v>
       </c>
       <c r="P114" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Q114" s="10" t="n">
-        <v>1.29797439999999</v>
+        <v>0</v>
       </c>
       <c r="R114" s="10" t="n">
         <v>0</v>
@@ -8636,26 +8639,26 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="20" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B115" s="21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C115" s="21" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D115" s="22" t="n">
         <v>1.6</v>
       </c>
       <c r="E115" s="8" t="n">
         <f aca="false">SUM(F115:I115)</f>
-        <v>1.1760019200002</v>
+        <v>1.35044088702466</v>
       </c>
       <c r="F115" s="10" t="n">
-        <v>1.1760019200002</v>
+        <v>0</v>
       </c>
       <c r="G115" s="10" t="n">
-        <v>0</v>
+        <v>1.35044088702466</v>
       </c>
       <c r="H115" s="10" t="n">
         <v>0</v>
@@ -8672,16 +8675,16 @@
         <v>0</v>
       </c>
       <c r="L115" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="M115" s="25" t="n">
-        <v>24</v>
+        <v>52</v>
+      </c>
+      <c r="M115" s="23" t="n">
+        <v>52</v>
       </c>
       <c r="N115" s="24" t="n">
-        <v>46300</v>
+        <v>46272</v>
       </c>
       <c r="O115" s="10" t="n">
-        <v>1.1760019200002</v>
+        <v>1.35044088702466</v>
       </c>
       <c r="P115" s="10" t="n">
         <v>0</v>
@@ -8699,23 +8702,23 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B116" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C116" s="21" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="D116" s="22" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="E116" s="8" t="n">
         <f aca="false">SUM(F116:I116)</f>
-        <v>1.095805</v>
+        <v>1.29797439999999</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>0</v>
+        <v>1.29797439999999</v>
       </c>
       <c r="G116" s="10" t="n">
         <v>0</v>
@@ -8724,33 +8727,33 @@
         <v>0</v>
       </c>
       <c r="I116" s="10" t="n">
-        <v>1.095805</v>
-      </c>
-      <c r="J116" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="10" t="n">
         <f aca="false">H116+I116</f>
-        <v>1.095805</v>
+        <v>0</v>
       </c>
       <c r="K116" s="11" t="n">
         <f aca="false">IF(E116&gt;0,J116/E116,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L116" s="12" t="n">
-        <v>185</v>
-      </c>
-      <c r="M116" s="28" t="n">
-        <v>185</v>
+        <v>27</v>
+      </c>
+      <c r="M116" s="25" t="n">
+        <v>27</v>
       </c>
       <c r="N116" s="24" t="n">
-        <v>46139</v>
+        <v>46297</v>
       </c>
       <c r="O116" s="10" t="n">
-        <v>1.095805</v>
+        <v>0</v>
       </c>
       <c r="P116" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Q116" s="10" t="n">
-        <v>0</v>
+        <v>1.29797439999999</v>
       </c>
       <c r="R116" s="10" t="n">
         <v>0</v>
@@ -8762,26 +8765,26 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="20" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B117" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C117" s="21" t="s">
-        <v>171</v>
+        <v>66</v>
       </c>
       <c r="D117" s="22" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="E117" s="8" t="n">
         <f aca="false">SUM(F117:I117)</f>
-        <v>1.0383108</v>
+        <v>1.1760019200002</v>
       </c>
       <c r="F117" s="10" t="n">
-        <v>0</v>
+        <v>1.1760019200002</v>
       </c>
       <c r="G117" s="10" t="n">
-        <v>1.0383108</v>
+        <v>0</v>
       </c>
       <c r="H117" s="10" t="n">
         <v>0</v>
@@ -8798,16 +8801,16 @@
         <v>0</v>
       </c>
       <c r="L117" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="M117" s="23" t="n">
-        <v>36</v>
+        <v>24</v>
+      </c>
+      <c r="M117" s="25" t="n">
+        <v>24</v>
       </c>
       <c r="N117" s="24" t="n">
-        <v>46288</v>
+        <v>46300</v>
       </c>
       <c r="O117" s="10" t="n">
-        <v>0</v>
+        <v>1.1760019200002</v>
       </c>
       <c r="P117" s="10" t="n">
         <v>0</v>
@@ -8816,7 +8819,7 @@
         <v>0</v>
       </c>
       <c r="R117" s="10" t="n">
-        <v>1.0383108</v>
+        <v>0</v>
       </c>
       <c r="S117" s="9" t="n">
         <f aca="false">COUNTIF(O117:R117,"&gt;0")</f>
@@ -8828,62 +8831,62 @@
         <v>172</v>
       </c>
       <c r="B118" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C118" s="21" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="D118" s="22" t="n">
         <v>2.5</v>
       </c>
       <c r="E118" s="8" t="n">
         <f aca="false">SUM(F118:I118)</f>
-        <v>0.983672499999989</v>
+        <v>1.095805</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>0.715932499999995</v>
+        <v>0</v>
       </c>
       <c r="G118" s="10" t="n">
-        <v>0.267739999999995</v>
+        <v>0</v>
       </c>
       <c r="H118" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I118" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="10" t="n">
+        <v>1.095805</v>
+      </c>
+      <c r="J118" s="26" t="n">
         <f aca="false">H118+I118</f>
-        <v>0</v>
+        <v>1.095805</v>
       </c>
       <c r="K118" s="11" t="n">
         <f aca="false">IF(E118&gt;0,J118/E118,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="12" t="n">
-        <v>23.2602339701475</v>
-      </c>
-      <c r="M118" s="23" t="n">
-        <v>40</v>
+        <v>185</v>
+      </c>
+      <c r="M118" s="28" t="n">
+        <v>185</v>
       </c>
       <c r="N118" s="24" t="n">
-        <v>46307</v>
+        <v>46139</v>
       </c>
       <c r="O118" s="10" t="n">
-        <v>0</v>
+        <v>1.095805</v>
       </c>
       <c r="P118" s="10" t="n">
-        <v>0.267739999999995</v>
+        <v>0</v>
       </c>
       <c r="Q118" s="10" t="n">
         <v>0</v>
       </c>
       <c r="R118" s="10" t="n">
-        <v>0.715932499999995</v>
+        <v>0</v>
       </c>
       <c r="S118" s="9" t="n">
         <f aca="false">COUNTIF(O118:R118,"&gt;0")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8891,62 +8894,62 @@
         <v>173</v>
       </c>
       <c r="B119" s="21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C119" s="21" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="D119" s="22" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E119" s="8" t="n">
         <f aca="false">SUM(F119:I119)</f>
-        <v>0.884169445298547</v>
+        <v>0.983672499999989</v>
       </c>
       <c r="F119" s="10" t="n">
-        <v>0</v>
+        <v>0.715932499999995</v>
       </c>
       <c r="G119" s="10" t="n">
-        <v>0</v>
+        <v>0.267739999999995</v>
       </c>
       <c r="H119" s="10" t="n">
-        <v>0.884169445298547</v>
+        <v>0</v>
       </c>
       <c r="I119" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J119" s="26" t="n">
+      <c r="J119" s="10" t="n">
         <f aca="false">H119+I119</f>
-        <v>0.884169445298547</v>
+        <v>0</v>
       </c>
       <c r="K119" s="11" t="n">
         <f aca="false">IF(E119&gt;0,J119/E119,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L119" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="M119" s="27" t="n">
-        <v>68</v>
+        <v>23.2602339701475</v>
+      </c>
+      <c r="M119" s="23" t="n">
+        <v>40</v>
       </c>
       <c r="N119" s="24" t="n">
-        <v>46256</v>
+        <v>46307</v>
       </c>
       <c r="O119" s="10" t="n">
-        <v>0.884169445298547</v>
+        <v>0</v>
       </c>
       <c r="P119" s="10" t="n">
-        <v>0</v>
+        <v>0.267739999999995</v>
       </c>
       <c r="Q119" s="10" t="n">
         <v>0</v>
       </c>
       <c r="R119" s="10" t="n">
-        <v>0</v>
+        <v>0.715932499999995</v>
       </c>
       <c r="S119" s="9" t="n">
         <f aca="false">COUNTIF(O119:R119,"&gt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8954,17 +8957,17 @@
         <v>174</v>
       </c>
       <c r="B120" s="21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C120" s="21" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="D120" s="22" t="n">
         <v>2</v>
       </c>
       <c r="E120" s="8" t="n">
         <f aca="false">SUM(F120:I120)</f>
-        <v>0.810000000000002</v>
+        <v>0.884169445298547</v>
       </c>
       <c r="F120" s="10" t="n">
         <v>0</v>
@@ -8973,30 +8976,30 @@
         <v>0</v>
       </c>
       <c r="H120" s="10" t="n">
-        <v>0</v>
+        <v>0.884169445298547</v>
       </c>
       <c r="I120" s="10" t="n">
-        <v>0.810000000000002</v>
+        <v>0</v>
       </c>
       <c r="J120" s="26" t="n">
         <f aca="false">H120+I120</f>
-        <v>0.810000000000002</v>
+        <v>0.884169445298547</v>
       </c>
       <c r="K120" s="11" t="n">
         <f aca="false">IF(E120&gt;0,J120/E120,0)</f>
         <v>1</v>
       </c>
       <c r="L120" s="12" t="n">
-        <v>121</v>
-      </c>
-      <c r="M120" s="28" t="n">
-        <v>121</v>
+        <v>68</v>
+      </c>
+      <c r="M120" s="27" t="n">
+        <v>68</v>
       </c>
       <c r="N120" s="24" t="n">
-        <v>46203</v>
+        <v>46256</v>
       </c>
       <c r="O120" s="10" t="n">
-        <v>0.810000000000002</v>
+        <v>0.884169445298547</v>
       </c>
       <c r="P120" s="10" t="n">
         <v>0</v>
@@ -9014,52 +9017,52 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="B121" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C121" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="B121" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C121" s="21" t="s">
-        <v>171</v>
-      </c>
       <c r="D121" s="22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E121" s="8" t="n">
         <f aca="false">SUM(F121:I121)</f>
-        <v>0.722176000000005</v>
+        <v>0.810000000000002</v>
       </c>
       <c r="F121" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G121" s="10" t="n">
-        <v>0.722176000000005</v>
+        <v>0</v>
       </c>
       <c r="H121" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I121" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" s="10" t="n">
+        <v>0.810000000000002</v>
+      </c>
+      <c r="J121" s="26" t="n">
         <f aca="false">H121+I121</f>
-        <v>0</v>
+        <v>0.810000000000002</v>
       </c>
       <c r="K121" s="11" t="n">
         <f aca="false">IF(E121&gt;0,J121/E121,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="M121" s="23" t="n">
-        <v>35</v>
+        <v>121</v>
+      </c>
+      <c r="M121" s="28" t="n">
+        <v>121</v>
       </c>
       <c r="N121" s="24" t="n">
-        <v>46289</v>
+        <v>46203</v>
       </c>
       <c r="O121" s="10" t="n">
-        <v>0</v>
+        <v>0.810000000000002</v>
       </c>
       <c r="P121" s="10" t="n">
         <v>0</v>
@@ -9068,7 +9071,7 @@
         <v>0</v>
       </c>
       <c r="R121" s="10" t="n">
-        <v>0.722176000000005</v>
+        <v>0</v>
       </c>
       <c r="S121" s="9" t="n">
         <f aca="false">COUNTIF(O121:R121,"&gt;0")</f>
@@ -9083,7 +9086,7 @@
         <v>18</v>
       </c>
       <c r="C122" s="21" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D122" s="22" t="n">
         <v>1.6</v>
@@ -9146,7 +9149,7 @@
         <v>18</v>
       </c>
       <c r="C123" s="21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D123" s="22" t="n">
         <v>2.5</v>
@@ -9209,7 +9212,7 @@
         <v>17</v>
       </c>
       <c r="C124" s="21" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D124" s="22" t="n">
         <v>2.2</v>
@@ -9335,7 +9338,7 @@
         <v>18</v>
       </c>
       <c r="C126" s="21" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D126" s="22" t="n">
         <v>4</v>
@@ -9398,7 +9401,7 @@
         <v>18</v>
       </c>
       <c r="C127" s="21" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D127" s="22" t="n">
         <v>1.6</v>
@@ -9461,7 +9464,7 @@
         <v>17</v>
       </c>
       <c r="C128" s="21" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D128" s="22" t="n">
         <v>1.2</v>
@@ -9524,7 +9527,7 @@
         <v>16</v>
       </c>
       <c r="C129" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D129" s="22" t="n">
         <v>4</v>
@@ -9587,7 +9590,7 @@
         <v>17</v>
       </c>
       <c r="C130" s="21" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D130" s="22" t="n">
         <v>4</v>
@@ -9651,11 +9654,11 @@
       <c r="D131" s="13"/>
       <c r="E131" s="15" t="n">
         <f aca="false">SUBTOTAL(9,E5:E130)</f>
-        <v>2813.82306871384</v>
+        <v>2889.17101111384</v>
       </c>
       <c r="F131" s="15" t="n">
         <f aca="false">SUBTOTAL(9,F5:F130)</f>
-        <v>2021.65412963058</v>
+        <v>2097.00207203058</v>
       </c>
       <c r="G131" s="15" t="n">
         <f aca="false">SUBTOTAL(9,G5:G130)</f>
@@ -9675,11 +9678,11 @@
       </c>
       <c r="K131" s="16" t="n">
         <f aca="false">IF(E131&gt;0,J131/E131,0)</f>
-        <v>0.104747195586381</v>
+        <v>0.102015448095753</v>
       </c>
       <c r="L131" s="17" t="n">
         <f aca="true">IF(E131&gt;0,SUMPRODUCT(SUBTOTAL(9,OFFSET(E5,ROW(E5:E130)-ROW(E5),0)),L5:L130)/E131,0)</f>
-        <v>31.0215908005722</v>
+        <v>30.2386447286033</v>
       </c>
       <c r="M131" s="13"/>
       <c r="N131" s="13"/>
@@ -9697,7 +9700,7 @@
       </c>
       <c r="R131" s="15" t="n">
         <f aca="false">SUBTOTAL(9,R5:R130)</f>
-        <v>742.1965613</v>
+        <v>817.5445037</v>
       </c>
       <c r="S131" s="13"/>
     </row>
@@ -9734,6 +9737,11 @@
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="18" t="s">
         <v>194</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="18" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Inventory-Ageing-SKU-wise-2026-10-29.xlsx
+++ b/reports/Inventory-Ageing-SKU-wise-2026-10-29.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Finished inventory ageing by section (MT) - as of 29-Oct-2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Every figure is a formula over the SKU-wise sheet. All sections together equal the Inventory Snapshot's current inventory for the same date.</t>
+    <t xml:space="preserve">Every figure is a formula over the SKU-wise sheet. Hyderabad, Lepakshi and NPMD equal the Inventory Snapshot of 29-Oct; Tapi also includes 75.3 MT of 28-Oct production entered after that Snapshot was built.</t>
   </si>
   <si>
     <t xml:space="preserve">Section</t>
